--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347328</t>
+          <t>346291</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89493</t>
+          <t>88456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BERTHA</t>
+          <t xml:space="preserve">ELIDA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">BARROETA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7225522448</t>
+          <t>5530348605</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GALEANA 432</t>
+          <t>EUCALIPTO</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>26-12-1972</t>
+          <t>23-04-1990</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>TITILINDA_13@HOTMAIL.COM</t>
+          <t>DRA.ALIDABM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-03-2026 12:03:01</t>
+          <t>24-02-2026 18:19:21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 12:08:35</t>
+          <t>03-03-2026 16:05:15</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01-03-2026 12:07:18</t>
+          <t>24-02-2026 18:31:40</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26320522768650004605</t>
+          <t>26320522845530005075</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347495</t>
+          <t>347328</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>BERTHA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,28 +752,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7224977744</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>7225522448</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GALEANA 432</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-09-2008</t>
+          <t>26-12-1972</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>LEBE0UF4T@GMAIL.COM</t>
+          <t>TITILINDA_13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 10:46:42</t>
+          <t>01-03-2026 12:03:01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -783,36 +787,44 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 11:29:30</t>
+          <t>01-03-2026 12:08:35</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:07:18</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,36 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26320522789250004739</t>
+          <t>26320522768650004605</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347598</t>
+          <t>347495</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ROMINA COLETTE</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANO </t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,28 +891,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7291089200</t>
+          <t>7224977744</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01-04-2008</t>
+          <t>12-09-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ROMICOLETTE31@GMAIL.COM</t>
+          <t>LEBE0UF4T@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:09</t>
+          <t>02-03-2026 10:46:42</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -910,44 +922,36 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:24</t>
+          <t>02-03-2026 11:29:30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 14:49:17</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,19 +959,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26320522795800004793</t>
+          <t>26320522789250004739</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -979,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347627</t>
+          <t>346879</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO </t>
+          <t>ESTEBAN ALBERTO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>FAZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,12 +1018,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7222502297</t>
+          <t>7226646634</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t xml:space="preserve">CERRADA SAN LAURA S/N </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1029,17 +1033,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-11-1993</t>
+          <t>28-06-1992</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FRANCISCO_9320@OUTLOOK.COM</t>
+          <t>TEBANFAZ0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:23:41</t>
+          <t>27-02-2026 08:52:39</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1049,44 +1053,36 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:17</t>
+          <t>03-03-2026 08:45:55</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:20:55</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,14 +1090,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26320522816360004905</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26320522833820004965</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>EMMANUEL  GONZALEZ  VILLANUEVA</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347317</t>
+          <t>347345</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>89510</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ARMANDO ALEJANDRO</t>
+          <t>KAREN NAOMI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t xml:space="preserve">MENDIETA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,32 +1157,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3310167684</t>
+          <t>7225360007</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALLENDE</t>
+          <t>ARETUSA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09-11-2000</t>
+          <t>12-08-2002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AA.SALAZARA@HOTMAIL.COM</t>
+          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:43</t>
+          <t>01-03-2026 12:58:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1188,22 +1192,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 11:18:24</t>
+          <t>01-03-2026 13:09:52</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 11:17:37</t>
+          <t>01-03-2026 13:08:09</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1233,14 +1237,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26320522767540004593</t>
+          <t>26320522769650004617</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1257,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347345</t>
+          <t>347300</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89510</t>
+          <t>89465</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KAREN NAOMI</t>
+          <t xml:space="preserve">IRMA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDIETA </t>
+          <t xml:space="preserve">ALBARRAN </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7225360007</t>
+          <t>7221158170</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ARETUSA</t>
+          <t>PUNGABARATO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,17 +1311,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-08-2002</t>
+          <t>24-12-1950</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
+          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 12:58:59</t>
+          <t>01-03-2026 10:36:01</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1327,22 +1331,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 13:09:52</t>
+          <t>01-03-2026 10:45:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-03-2026 13:08:09</t>
+          <t>01-03-2026 10:43:49</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,14 +1376,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26320522769650004617</t>
+          <t>26320522766920004585</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1396,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>343681</t>
+          <t>347333</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS JESUS </t>
+          <t xml:space="preserve">ERIKA JAZMIN </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DEBEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>VALDESPINO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1435,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7222287294</t>
+          <t>7224674810</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SAN ISIDRO 13</t>
+          <t>CALLE CASCO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>15-02-1969</t>
+          <t>31-08-1984</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
+          <t>ERICKA.JRV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14-02-2026 09:58:23</t>
+          <t>01-03-2026 12:15:48</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1466,32 +1470,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-03-2026 11:22:35</t>
+          <t>01-03-2026 12:21:55</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>14-02-2026 10:10:26</t>
+          <t>01-03-2026 12:19:40</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1511,14 +1515,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26320522767610004596</t>
+          <t>26320522768910004609</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1535,12 +1539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>346076</t>
+          <t>343681</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>88241</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JAVIER DE JESUS</t>
+          <t xml:space="preserve">LUIS JESUS </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DEBEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,12 +1574,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5619333968</t>
+          <t>7222287294</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5 DE MAYO 712</t>
+          <t>SAN ISIDRO 13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1585,17 +1589,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>03-03-1990</t>
+          <t>15-02-1969</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
+          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>24-02-2026 07:00:04</t>
+          <t>14-02-2026 09:58:23</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1620,17 +1624,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 06:34:23</t>
+          <t>01-03-2026 11:22:35</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 06:33:27</t>
+          <t>14-02-2026 10:10:26</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1650,19 +1654,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26320522780780004667</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522767610004596</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>649</t>
@@ -1682,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347165</t>
+          <t>346076</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89330</t>
+          <t>88241</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t>JAVIER DE JESUS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALMAZAN</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,32 +1713,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7221565585</t>
+          <t>5619333968</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>5 DE MAYO 712</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-07-1990</t>
+          <t>03-03-1990</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AGUS.TOL13@GMAIL.COM</t>
+          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28-02-2026 09:37:39</t>
+          <t>24-02-2026 07:00:04</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1752,32 +1748,32 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 10:34:40</t>
+          <t>02-03-2026 06:34:23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>28-03-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>28-02-2026 09:50:05</t>
+          <t>02-03-2026 06:33:27</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1797,14 +1793,22 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26320522766810004583</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26320522780780004667</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1821,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347298</t>
+          <t>347165</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>89330</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ROBERTO AARON</t>
+          <t>AGUSTIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>ALMAZAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,32 +1860,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7225105138</t>
+          <t>7221565585</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GUMERCINDO</t>
+          <t>TENANCINGO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-02-1988</t>
+          <t>14-07-1990</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ROBERTOGALINDO9@GMAIL.COM</t>
+          <t>AGUS.TOL13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:27:15</t>
+          <t>28-02-2026 09:37:39</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1906,17 +1910,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:48</t>
+          <t>01-03-2026 10:34:40</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>28-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:37</t>
+          <t>28-02-2026 09:50:05</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1936,7 +1940,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26320522766780004582</t>
+          <t>26320522766810004583</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1960,12 +1964,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347525</t>
+          <t>347298</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89690</t>
+          <t>89463</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1979,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>ROBERTO AARON</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,12 +1999,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7222641163</t>
+          <t>7225105138</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JUAN ALDAMA</t>
+          <t>GUMERCINDO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2010,17 +2014,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>07-02-1980</t>
+          <t>28-02-1988</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FME28@HOTMAIL.COM</t>
+          <t>ROBERTOGALINDO9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:58</t>
+          <t>01-03-2026 10:27:15</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2045,17 +2049,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 12:33:33</t>
+          <t>01-03-2026 10:31:48</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 12:32:29</t>
+          <t>01-03-2026 10:30:37</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2075,7 +2079,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26320522791260004756</t>
+          <t>26320522766780004582</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2087,24 +2091,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347333</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2114,17 +2118,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA JAZMIN </t>
+          <t>ARMANDO ALEJANDRO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VALDESPINO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2134,32 +2138,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7224674810</t>
+          <t>3310167684</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CALLE CASCO</t>
+          <t>ALLENDE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31-08-1984</t>
+          <t>09-11-2000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ERICKA.JRV@GMAIL.COM</t>
+          <t>AA.SALAZARA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>01-03-2026 12:15:48</t>
+          <t>01-03-2026 11:12:43</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2169,22 +2173,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:55</t>
+          <t>01-03-2026 11:18:24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2194,7 +2198,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>01-03-2026 12:19:40</t>
+          <t>01-03-2026 11:17:37</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2214,14 +2218,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26320522768910004609</t>
+          <t>26320522767540004593</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2238,12 +2242,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347300</t>
+          <t>347598</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89465</t>
+          <t>89763</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2253,17 +2257,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRMA </t>
+          <t>ROMINA COLETTE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBARRAN </t>
+          <t xml:space="preserve">CASTELLANO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2273,14 +2277,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7221158170</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PUNGABARATO</t>
-        </is>
-      </c>
+          <t>7291089200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2288,17 +2288,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24-12-1950</t>
+          <t>01-04-2008</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
+          <t>ROMICOLETTE31@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>01-03-2026 10:36:01</t>
+          <t>02-03-2026 14:41:09</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>01-03-2026 10:45:05</t>
+          <t>02-03-2026 14:50:24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>01-03-2026 10:43:49</t>
+          <t>02-03-2026 14:49:17</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26320522766920004585</t>
+          <t>26320522795800004793</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2365,24 +2365,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>347627</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>88239</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS JACINTO </t>
+          <t xml:space="preserve">FRANCISCO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DEL ANGEL</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BALLESTEROS</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7223806506</t>
+          <t>7222502297</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CALLE CIENTIFICOS 109</t>
+          <t>PRIVADA AVELLANO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16-06-1980</t>
+          <t>20-11-1993</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CARLOSRO08@HOTMAIL.COM</t>
+          <t>FRANCISCO_9320@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>24-02-2026 06:56:28</t>
+          <t>02-03-2026 15:23:41</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 06:28:17</t>
+          <t>02-03-2026 19:23:17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 06:27:05</t>
+          <t>02-03-2026 19:20:55</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2492,19 +2492,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26320522780570004665</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522816360004905</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>649</t>
@@ -2524,12 +2516,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347284</t>
+          <t>347824</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2539,17 +2531,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t xml:space="preserve">MONSERRAT </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PICHARDO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2559,32 +2551,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5543692402</t>
+          <t>7291230160</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JARDINES DE SAN MATEO</t>
+          <t xml:space="preserve">MARIANO MATAMOROS 62 </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03-11-1988</t>
+          <t>08-11-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
+          <t>PICHLEDES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>01-03-2026 09:28:32</t>
+          <t>02-03-2026 18:28:58</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2594,32 +2586,32 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>01-03-2026 09:36:17</t>
+          <t>03-03-2026 05:39:04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>01-03-2026 09:34:02</t>
+          <t>03-03-2026 05:38:01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2639,14 +2631,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26320522765720004564</t>
+          <t>26320522823530004929</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2663,12 +2655,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347314</t>
+          <t>346074</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2678,17 +2670,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL </t>
+          <t xml:space="preserve">CARLOS JACINTO </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>DEL ANGEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>BALLESTEROS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2698,12 +2690,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7226722765</t>
+          <t>7223806506</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t>CALLE CIENTIFICOS 109</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2713,17 +2705,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>08-03-2001</t>
+          <t>16-06-1980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MANULOP632@GMAIL.COM</t>
+          <t>CARLOSRO08@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>01-03-2026 11:10:07</t>
+          <t>24-02-2026 06:56:28</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2748,7 +2740,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 10:26:20</t>
+          <t>02-03-2026 06:28:17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2758,7 +2750,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>02-03-2026 06:27:05</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2778,7 +2770,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26320522787680004716</t>
+          <t>26320522780570004665</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2788,7 +2780,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2810,12 +2802,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347588</t>
+          <t>346632</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89753</t>
+          <t>88797</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2825,17 +2817,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAYDI DIANA </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2845,28 +2837,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7225315083</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>7224064130</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO DE PAULA 58</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-10-1988</t>
+          <t>01-01-1971</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LGARCIA@FIRA.GOG</t>
+          <t>A.CHAVEZ71@LIVE.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 14:25:22</t>
+          <t>26-02-2026 05:55:50</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2876,36 +2872,44 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 14:28:47</t>
+          <t>03-03-2026 05:48:40</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:47:42</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2913,14 +2917,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26320522794880004783</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26320522823730004932</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2937,12 +2949,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347625</t>
+          <t>347525</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89790</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2952,17 +2964,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUIS ALONSO</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2972,12 +2984,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7227504088</t>
+          <t>7222641163</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t>JUAN ALDAMA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2987,17 +2999,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-09-2011</t>
+          <t>07-02-1980</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KARLAGABY14@HOTMAIL.COM</t>
+          <t>FME28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:56</t>
+          <t>02-03-2026 12:04:58</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3007,22 +3019,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:30:47</t>
+          <t>02-03-2026 12:33:33</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3032,7 +3044,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:29:36</t>
+          <t>02-03-2026 12:32:29</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3042,7 +3054,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3052,36 +3064,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26320522816940004906</t>
+          <t>26320522791260004756</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347528</t>
+          <t>347625</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89693</t>
+          <t>89790</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGE </t>
+          <t xml:space="preserve"> LUIS ALONSO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BANDERAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3111,12 +3123,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7292940204</t>
+          <t>7227504088</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN ALDAMA </t>
+          <t>PRIVADA AVELLANO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3126,17 +3138,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>15-09-2011</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JORGESALAZAR228@HOTMAIL.COM</t>
+          <t>KARLAGABY14@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:41</t>
+          <t>02-03-2026 15:21:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3146,22 +3158,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:28</t>
+          <t>02-03-2026 19:30:47</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3171,7 +3183,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:43</t>
+          <t>02-03-2026 19:29:36</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3181,7 +3193,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3191,14 +3203,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26320522790800004750</t>
+          <t>26320522816940004906</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3215,12 +3227,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347561</t>
+          <t>347588</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3230,17 +3242,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t xml:space="preserve">LAYDI DIANA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISLAS </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3250,32 +3262,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5536313160</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>NAUCAL</t>
-        </is>
-      </c>
+          <t>7225315083</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>02-03-1994</t>
+          <t>06-10-1988</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
+          <t>LGARCIA@FIRA.GOG</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:04</t>
+          <t>02-03-2026 14:25:22</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3285,44 +3293,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:44</t>
+          <t>02-03-2026 14:28:47</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:08:36</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3330,14 +3330,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26320522815880004904</t>
+          <t>26320522794880004783</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3354,12 +3354,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347530</t>
+          <t>347528</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89695</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ZEPETA</t>
+          <t>BANDERAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3389,32 +3389,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7225675528</t>
+          <t>7292940204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CARLOTA</t>
+          <t xml:space="preserve">JUAN ALDAMA </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11-01-2006</t>
+          <t>28-02-1997</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>VALERIAZEPETAA1@GMAIL.COM</t>
+          <t>JORGESALAZAR228@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:09:14</t>
+          <t>02-03-2026 12:07:41</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:37:18</t>
+          <t>02-03-2026 12:18:28</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:50</t>
+          <t>02-03-2026 12:13:43</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26320522791400004759</t>
+          <t>26320522790800004750</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3481,24 +3481,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347463</t>
+          <t>347561</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3508,17 +3508,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELBA SUSANA </t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IBANCOVICHI</t>
+          <t xml:space="preserve">ISLAS </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3528,32 +3528,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7222899520</t>
+          <t>5536313160</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CERRADA DE LUMARAN 118</t>
+          <t>NAUCAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>02-03-1994</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MIBANCOVICHI@GMAIL.COM</t>
+          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:23:35</t>
+          <t>02-03-2026 13:19:04</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3563,22 +3563,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:29:01</t>
+          <t>02-03-2026 19:15:44</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:42</t>
+          <t>02-03-2026 19:08:36</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3608,14 +3608,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26320522785920004701</t>
+          <t>26320522815880004904</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347833</t>
+          <t>347463</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89998</t>
+          <t>89628</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KARLA ISABEL</t>
+          <t xml:space="preserve">ELBA SUSANA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>IBANCOVICHI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7226289693</t>
+          <t>7222899520</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BOSQUE DE CAPULINES</t>
+          <t>CERRADA DE LUMARAN 118</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3682,17 +3682,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-02-1993</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>KARLA080293@GMAIL.COM</t>
+          <t>MIBANCOVICHI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:34:40</t>
+          <t>02-03-2026 09:23:35</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:06</t>
+          <t>02-03-2026 09:29:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:45:03</t>
+          <t>02-03-2026 09:27:42</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26320522813850004898</t>
+          <t>26320522785920004701</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3771,12 +3771,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347611</t>
+          <t>347628</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89776</t>
+          <t>89793</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GAEL VALENTIN</t>
+          <t xml:space="preserve">LUIS RAUL </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLANUEVA </t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7203337010</t>
+          <t>7298256500</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">REP DE NICARAGUA </t>
+          <t>IGNACIO ALLENDE 22</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02-12-2012</t>
+          <t>26-11-1994</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>VALENTINGAEL12@GMAIL.COM</t>
+          <t>LUISRAUL.AC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 14:59:03</t>
+          <t>02-03-2026 15:24:01</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3841,32 +3841,32 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:51</t>
+          <t>03-03-2026 16:41:32</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:01</t>
+          <t>03-03-2026 16:40:45</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3886,14 +3886,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26320522796410004796</t>
+          <t>26320522847660005096</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3910,12 +3910,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347316</t>
+          <t>347611</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89481</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EDUARD</t>
+          <t>GAEL VALENTIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">VILLANUEVA </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7226915455</t>
+          <t>7203337010</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t xml:space="preserve">REP DE NICARAGUA </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-10-2003</t>
+          <t>02-12-2012</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
+          <t>VALENTINGAEL12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:17</t>
+          <t>02-03-2026 14:59:03</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 05:23:00</t>
+          <t>02-03-2026 15:04:51</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-03-2026 05:21:41</t>
+          <t>02-03-2026 15:04:01</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4025,19 +4025,11 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26320522773140004645</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
-        </is>
-      </c>
+          <t>26320522796410004796</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>649</t>
@@ -4057,12 +4049,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347739</t>
+          <t>347530</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89904</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4072,17 +4064,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EDUARDO ELHIU</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>ZEPETA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4092,28 +4084,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7292264814</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>7225675528</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CARLOTA</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18-07-1998</t>
+          <t>11-01-2006</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
+          <t>VALERIAZEPETAA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:34</t>
+          <t>02-03-2026 12:09:14</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4123,36 +4119,44 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:05</t>
+          <t>02-03-2026 12:37:18</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:36:50</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4160,36 +4164,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26320522806550004859</t>
+          <t>26320522791400004759</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347851</t>
+          <t>347992</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>90157</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4199,17 +4203,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RICARDO AXEL</t>
+          <t xml:space="preserve">EUNICE </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4219,32 +4223,28 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7227717603</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
-        </is>
-      </c>
+          <t>7226818060</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30-09-1993</t>
+          <t>18-09-1992</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AXELOR.14@GMAIL.COM</t>
+          <t>EUNICESAN9218@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 18:48:23</t>
+          <t>03-03-2026 09:47:15</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4254,44 +4254,36 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:49</t>
+          <t>03-03-2026 09:48:47</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:52:27</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4299,22 +4291,1936 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26320522814360004903</t>
+          <t>26320522835410004978</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347994</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90159</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEMETRIO </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALVILLO </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3369637522</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22-07-1987</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DEMETRIOCH9287@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:54:17</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:57:00</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26320522835680004982</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348036</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90201</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>RAYON</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5519545111</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>02-04-2001</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LUISBRITHIS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>03-03-2026 12:54:24</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:06:20</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:05:40</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26320522839610005033</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348126</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90291</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN ALBERTO </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>7222842150</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CORREGIDORA2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>28-08-1974</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ALBERTO2874@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:38:02</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:48:12</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:46:41</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26320522848120005102</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348268</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90433</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ALDEMAR RAYMUNDO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VALDES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5623590912</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MORELOS</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>18-11-1971</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>RAYMUNDOVALDES30@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:29:01</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:35:47</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:34:01</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26320522859400005179</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348122</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90287</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ALBERTO DANIEL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIOS </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHAPARRO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5654900068</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BOSQUES DE PIRULES</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>14-09-2001</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ALBERTDANY@HOTMAIL.ES</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:33:05</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:50:09</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:49:36</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26320522848180005103</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>347284</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>89449</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMMANUEL </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BARRERA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5543692402</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>JARDINES DE SAN MATEO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>03-11-1988</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>01-03-2026 09:28:32</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>01-03-2026 09:36:17</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>01-03-2026 09:34:02</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26320522765720004564</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>347314</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>89479</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANUEL </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>7226722765</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FRESNOS 34</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>08-03-2001</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>MANULOP632@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:10:07</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:26:20</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:24:46</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26320522787680004716</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>347316</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>89481</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EDUARD</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>7226915455</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FRESNOS 34</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>21-10-2003</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:12:17</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:23:00</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:21:41</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26320522773140004645</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>347851</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>90016</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RICARDO AXEL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OROZCO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NIETO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>7227717603</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>30-09-1993</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AXELOR.14@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:48:23</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:52:49</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:52:27</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26320522814360004903</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>347991</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>90156</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ABRAHAM MILLEL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NAVARRO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>7226508332</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>10-08-1999</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>HILLELDRUMS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:47:09</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:49:39</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26320522835460004979</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>347833</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>89998</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>KARLA ISABEL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7226289693</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BOSQUE DE CAPULINES</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>08-02-1993</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>KARLA080293@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:34:40</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:47:06</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:45:03</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26320522813850004898</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>348120</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90285</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BRENDA AMPARO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>YEPEZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7221680849</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>IGANACIO ALLENDE 22</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>28-04-1993</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BREN_LOP@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:29:43</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:45:46</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:44:59</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26320522847960005100</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>347739</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>89904</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EDUARDO ELHIU</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7292264814</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>18-07-1998</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:24:34</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:27:05</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26320522806550004859</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>347938</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90103</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAÑON </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BALADO </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7221689741</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11-02-1988</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CARLOS.BALADO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:15:55</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1 MES $999</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:18:50</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26320522830160004936</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346291</t>
+          <t>331392</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIDA </t>
+          <t xml:space="preserve">DANNA JIMENA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARROETA </t>
+          <t>LOREDO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GODINEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5530348605</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>EUCALIPTO</t>
-        </is>
-      </c>
+          <t>7225941695</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -628,64 +624,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23-04-1990</t>
+          <t>01-11-2007</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DRA.ALIDABM@GMAIL.COM</t>
+          <t>DONA000ROSITA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24-02-2026 18:19:21</t>
+          <t>31-12-2025 12:03:45</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>200 la viga tlalnepantla</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 X 2 MESES POR $1,198 METEPEC</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>399.33</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 16:05:15</t>
+          <t>04-03-2026 12:14:27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>24-02-2026 18:31:40</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26320522845530005075</t>
+          <t>26320522880230005286</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347328</t>
+          <t>346133</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89493</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BERTHA</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +740,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7225522448</t>
+          <t>7224444385</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GALEANA 432</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26-12-1972</t>
+          <t>03-10-1960</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>TITILINDA_13@HOTMAIL.COM</t>
+          <t>GAGUILARM1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 12:03:01</t>
+          <t>24-02-2026 12:15:50</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -787,32 +775,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 12:08:35</t>
+          <t>05-03-2026 11:31:05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 12:07:18</t>
+          <t>05-03-2026 11:30:17</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -822,7 +810,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -832,14 +820,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26320522768650004605</t>
+          <t>26320522913700005501</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -856,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347495</t>
+          <t>346879</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>ESTEBAN ALBERTO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>FAZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,10 +879,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7224977744</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>7226646634</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERRADA SAN LAURA S/N </t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -902,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-09-2008</t>
+          <t>28-06-1992</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LEBE0UF4T@GMAIL.COM</t>
+          <t>TEBANFAZ0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 10:46:42</t>
+          <t>27-02-2026 08:52:39</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -927,22 +919,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:29:30</t>
+          <t>03-03-2026 08:45:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -959,36 +951,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26320522789250004739</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26320522833820004965</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>EMMANUEL  GONZALEZ  VILLANUEVA</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346879</t>
+          <t>346131</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>88296</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESTEBAN ALBERTO</t>
+          <t xml:space="preserve">CLAUDIA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>BEAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAZ</t>
+          <t>ARMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7226646634</t>
+          <t>7224444382</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERRADA SAN LAURA S/N </t>
+          <t>MOCTEZUMA 729</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-06-1992</t>
+          <t>08-04-1964</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TEBANFAZ0@GMAIL.COM</t>
+          <t>CLAUDIA.BARMAND@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27-02-2026 08:52:39</t>
+          <t>24-02-2026 12:13:21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1053,36 +1053,44 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 08:45:55</t>
+          <t>05-03-2026 11:28:16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:25:42</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,22 +1098,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26320522833820004965</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>EMMANUEL  GONZALEZ  VILLANUEVA</t>
-        </is>
-      </c>
+          <t>26320522913610005500</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1122,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347345</t>
+          <t>347333</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89510</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAREN NAOMI</t>
+          <t xml:space="preserve">ERIKA JAZMIN </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDIETA </t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>VALDESPINO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7225360007</t>
+          <t>7224674810</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ARETUSA</t>
+          <t>CALLE CASCO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>12-08-2002</t>
+          <t>31-08-1984</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
+          <t>ERICKA.JRV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:58:59</t>
+          <t>01-03-2026 12:15:48</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 13:09:52</t>
+          <t>01-03-2026 12:21:55</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 13:08:09</t>
+          <t>01-03-2026 12:19:40</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26320522769650004617</t>
+          <t>26320522768910004609</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1261,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347300</t>
+          <t>325426</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89465</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRMA </t>
+          <t>BRISA ELIZABETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBARRAN </t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7221158170</t>
+          <t>7223886398</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PUNGABARATO</t>
+          <t>MARCELINO SUAREZ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1311,24 +1311,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-12-1950</t>
+          <t>06-12-1987</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
+          <t>BRISBENTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:36:01</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 HE</t>
-        </is>
-      </c>
+          <t>26-11-2025 13:56:12</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1336,27 +1332,27 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO 12 MESES $599 METEPEC</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:45:05</t>
+          <t>05-03-2026 17:00:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-03-2026 10:43:49</t>
+          <t>26-01-2026 16:46:47</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1366,7 +1362,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1376,36 +1372,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26320522766920004585</t>
+          <t>26320522922340005617</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347333</t>
+          <t>327753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA JAZMIN </t>
+          <t xml:space="preserve">LUIS DANIEL </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VALDESPINO</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,67 +1431,63 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7224674810</t>
+          <t>5534444945</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CALLE CASCO</t>
+          <t>DIEGO RIVERA 305</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31-08-1984</t>
+          <t>16-05-1983</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ERICKA.JRV@GMAIL.COM</t>
+          <t>LDANIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:15:48</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 HE</t>
-        </is>
-      </c>
+          <t>06-12-2025 09:36:12</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $599 METEPEC</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:55</t>
+          <t>05-03-2026 11:00:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:19:40</t>
+          <t>06-12-2025 09:42:36</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1505,7 +1497,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1515,14 +1507,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26320522768910004609</t>
+          <t>26320522911100005478</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1539,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>343681</t>
+          <t>337277</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS JESUS </t>
+          <t>JAEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DEBEZ</t>
+          <t>MARURI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>MARURI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,12 +1566,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7222287294</t>
+          <t>7221166978</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SAN ISIDRO 13</t>
+          <t>EL MOLINO 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1589,17 +1581,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-02-1969</t>
+          <t>22-03-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
+          <t>YAELMARURI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:58:23</t>
+          <t>23-01-2026 14:29:06</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1609,32 +1601,32 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-03-2026 11:22:35</t>
+          <t>05-03-2026 14:11:05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14-02-2026 10:10:26</t>
+          <t>05-03-2026 14:10:09</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1654,14 +1646,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26320522767610004596</t>
+          <t>26320522916610005540</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1678,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>346076</t>
+          <t>346074</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88241</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JAVIER DE JESUS</t>
+          <t xml:space="preserve">CARLOS JACINTO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DEL ANGEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t>BALLESTEROS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,12 +1705,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5619333968</t>
+          <t>7223806506</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5 DE MAYO 712</t>
+          <t>CALLE CIENTIFICOS 109</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1728,17 +1720,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-03-1990</t>
+          <t>16-06-1980</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
+          <t>CARLOSRO08@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24-02-2026 07:00:04</t>
+          <t>24-02-2026 06:56:28</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1763,7 +1755,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:34:23</t>
+          <t>02-03-2026 06:28:17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1773,7 +1765,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:33:27</t>
+          <t>02-03-2026 06:27:05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1793,7 +1785,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26320522780780004667</t>
+          <t>26320522780570004665</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1825,12 +1817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347165</t>
+          <t>347588</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89330</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1832,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t xml:space="preserve">LAYDI DIANA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALMAZAN</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,14 +1852,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7221565585</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>TENANCINGO</t>
-        </is>
-      </c>
+          <t>7225315083</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1875,17 +1863,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14-07-1990</t>
+          <t>06-10-1988</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>AGUS.TOL13@GMAIL.COM</t>
+          <t>LGARCIA@FIRA.GOG</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>28-02-2026 09:37:39</t>
+          <t>02-03-2026 14:25:22</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1895,44 +1883,36 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 10:34:40</t>
+          <t>02-03-2026 14:28:47</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>28-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>28-02-2026 09:50:05</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1940,14 +1920,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26320522766810004583</t>
+          <t>26320522794880004783</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1964,12 +1944,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347298</t>
+          <t>347345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>89510</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1979,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ROBERTO AARON</t>
+          <t>KAREN NAOMI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t xml:space="preserve">MENDIETA </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1999,32 +1979,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7225105138</t>
+          <t>7225360007</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GUMERCINDO</t>
+          <t>ARETUSA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28-02-1988</t>
+          <t>12-08-2002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ROBERTOGALINDO9@GMAIL.COM</t>
+          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-03-2026 10:27:15</t>
+          <t>01-03-2026 12:58:59</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2039,17 +2019,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:48</t>
+          <t>01-03-2026 13:09:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2059,7 +2039,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:37</t>
+          <t>01-03-2026 13:08:09</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2069,7 +2049,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2079,36 +2059,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26320522766780004582</t>
+          <t>26320522769650004617</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347317</t>
+          <t>347528</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2118,7 +2098,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARMANDO ALEJANDRO</t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2128,7 +2108,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>BANDERAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2138,12 +2118,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3310167684</t>
+          <t>7292940204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALLENDE</t>
+          <t xml:space="preserve">JUAN ALDAMA </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2153,17 +2133,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>09-11-2000</t>
+          <t>28-02-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>AA.SALAZARA@HOTMAIL.COM</t>
+          <t>JORGESALAZAR228@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:43</t>
+          <t>02-03-2026 12:07:41</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2173,32 +2153,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>01-03-2026 11:18:24</t>
+          <t>02-03-2026 12:18:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>01-03-2026 11:17:37</t>
+          <t>02-03-2026 12:13:43</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2218,14 +2198,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26320522767540004593</t>
+          <t>26320522790800004750</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2242,12 +2222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347598</t>
+          <t>347561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2257,17 +2237,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROMINA COLETTE</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANO </t>
+          <t xml:space="preserve">ISLAS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2277,28 +2257,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7291089200</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>5536313160</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NAUCAL</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>01-04-2008</t>
+          <t>02-03-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ROMICOLETTE31@GMAIL.COM</t>
+          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:09</t>
+          <t>02-03-2026 13:19:04</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2308,22 +2292,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:24</t>
+          <t>02-03-2026 19:15:44</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2333,7 +2317,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:49:17</t>
+          <t>02-03-2026 19:08:36</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2353,36 +2337,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26320522795800004793</t>
+          <t>26320522815880004904</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347627</t>
+          <t>347300</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>89465</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2376,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO </t>
+          <t xml:space="preserve">IRMA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t xml:space="preserve">ALBARRAN </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,32 +2396,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7222502297</t>
+          <t>7221158170</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t>PUNGABARATO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20-11-1993</t>
+          <t>24-12-1950</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FRANCISCO_9320@OUTLOOK.COM</t>
+          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 15:23:41</t>
+          <t>01-03-2026 10:36:01</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2462,17 +2446,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:17</t>
+          <t>01-03-2026 10:45:05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:20:55</t>
+          <t>01-03-2026 10:43:49</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2492,7 +2476,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26320522816360004905</t>
+          <t>26320522766920004585</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2516,12 +2500,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347824</t>
+          <t>347463</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89989</t>
+          <t>89628</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2531,17 +2515,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONSERRAT </t>
+          <t xml:space="preserve">ELBA SUSANA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PICHARDO</t>
+          <t>IBANCOVICHI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LEDESMA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2551,12 +2535,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7291230160</t>
+          <t>7222899520</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANO MATAMOROS 62 </t>
+          <t>CERRADA DE LUMARAN 118</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2566,17 +2550,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>08-11-2000</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PICHLEDES@GMAIL.COM</t>
+          <t>MIBANCOVICHI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 18:28:58</t>
+          <t>02-03-2026 09:23:35</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2586,32 +2570,32 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 05:39:04</t>
+          <t>02-03-2026 09:29:01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 05:38:01</t>
+          <t>02-03-2026 09:27:42</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2631,14 +2615,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26320522823530004929</t>
+          <t>26320522785920004701</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2655,12 +2639,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>346291</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>88239</t>
+          <t>88456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2670,17 +2654,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS JACINTO </t>
+          <t xml:space="preserve">ELIDA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DEL ANGEL</t>
+          <t xml:space="preserve">BARROETA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BALLESTEROS</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2690,32 +2674,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7223806506</t>
+          <t>5530348605</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CALLE CIENTIFICOS 109</t>
+          <t>EUCALIPTO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16-06-1980</t>
+          <t>23-04-1990</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CARLOSRO08@HOTMAIL.COM</t>
+          <t>DRA.ALIDABM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24-02-2026 06:56:28</t>
+          <t>24-02-2026 18:19:21</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2725,32 +2709,32 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 06:28:17</t>
+          <t>03-03-2026 16:05:15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 06:27:05</t>
+          <t>24-02-2026 18:31:40</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2770,22 +2754,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26320522780570004665</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522845530005075</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2802,12 +2778,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>346632</t>
+          <t>347328</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>88797</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2817,17 +2793,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>BERTHA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2837,32 +2813,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7224064130</t>
+          <t>7225522448</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE PAULA 58</t>
+          <t>GALEANA 432</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>01-01-1971</t>
+          <t>26-12-1972</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>A.CHAVEZ71@LIVE.COM</t>
+          <t>TITILINDA_13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26-02-2026 05:55:50</t>
+          <t>01-03-2026 12:03:01</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2877,27 +2853,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 05:48:40</t>
+          <t>01-03-2026 12:08:35</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>03-03-2026 05:47:42</t>
+          <t>01-03-2026 12:07:18</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2917,22 +2893,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26320522823730004932</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522768650004605</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2949,12 +2917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347525</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89690</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2964,17 +2932,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>ARMANDO ALEJANDRO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2984,12 +2952,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7222641163</t>
+          <t>3310167684</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JUAN ALDAMA</t>
+          <t>ALLENDE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2999,17 +2967,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-02-1980</t>
+          <t>09-11-2000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>FME28@HOTMAIL.COM</t>
+          <t>AA.SALAZARA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:58</t>
+          <t>01-03-2026 11:12:43</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3019,32 +2987,32 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 12:33:33</t>
+          <t>01-03-2026 11:18:24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 12:32:29</t>
+          <t>01-03-2026 11:17:37</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3064,36 +3032,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26320522791260004756</t>
+          <t>26320522767540004593</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347625</t>
+          <t>347530</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89790</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3103,17 +3071,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUIS ALONSO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ZEPETA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3123,32 +3091,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7227504088</t>
+          <t>7225675528</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t>CARLOTA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15-09-2011</t>
+          <t>11-01-2006</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>KARLAGABY14@HOTMAIL.COM</t>
+          <t>VALERIAZEPETAA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:56</t>
+          <t>02-03-2026 12:09:14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3158,22 +3126,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:30:47</t>
+          <t>02-03-2026 12:37:18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3183,7 +3151,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:29:36</t>
+          <t>02-03-2026 12:36:50</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3193,7 +3161,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3203,36 +3171,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26320522816940004906</t>
+          <t>26320522791400004759</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347588</t>
+          <t>346632</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89753</t>
+          <t>88797</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3242,17 +3210,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAYDI DIANA </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3262,28 +3230,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7225315083</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>7224064130</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO DE PAULA 58</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-10-1988</t>
+          <t>01-01-1971</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>LGARCIA@FIRA.GOG</t>
+          <t>A.CHAVEZ71@LIVE.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 14:25:22</t>
+          <t>26-02-2026 05:55:50</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3293,36 +3265,44 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 14:28:47</t>
+          <t>03-03-2026 05:48:40</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:47:42</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3330,14 +3310,22 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26320522794880004783</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26320522823730004932</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3354,12 +3342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347528</t>
+          <t>347284</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89693</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3369,17 +3357,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGE </t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BANDERAS</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3389,12 +3377,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7292940204</t>
+          <t>5543692402</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN ALDAMA </t>
+          <t>JARDINES DE SAN MATEO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3404,17 +3392,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>03-11-1988</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>JORGESALAZAR228@HOTMAIL.COM</t>
+          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:41</t>
+          <t>01-03-2026 09:28:32</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3424,32 +3412,32 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:28</t>
+          <t>01-03-2026 09:36:17</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:43</t>
+          <t>01-03-2026 09:34:02</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3459,7 +3447,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3469,14 +3457,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26320522790800004750</t>
+          <t>26320522765720004564</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3493,12 +3481,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347561</t>
+          <t>347314</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>89479</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3508,17 +3496,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t xml:space="preserve">MANUEL </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISLAS </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3528,12 +3516,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5536313160</t>
+          <t>7226722765</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NAUCAL</t>
+          <t>FRESNOS 34</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3543,17 +3531,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-03-1994</t>
+          <t>08-03-2001</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
+          <t>MANULOP632@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:04</t>
+          <t>01-03-2026 11:10:07</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3563,22 +3551,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:44</t>
+          <t>02-03-2026 10:26:20</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3588,7 +3576,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 19:08:36</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3598,7 +3586,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3608,14 +3596,22 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26320522815880004904</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26320522787680004716</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3632,12 +3628,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347463</t>
+          <t>347316</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>89481</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3647,17 +3643,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELBA SUSANA </t>
+          <t>EDUARD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IBANCOVICHI</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3667,32 +3663,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7222899520</t>
+          <t>7226915455</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CERRADA DE LUMARAN 118</t>
+          <t>FRESNOS 34</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>21-10-2003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MIBANCOVICHI@GMAIL.COM</t>
+          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 09:23:35</t>
+          <t>01-03-2026 11:12:17</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3717,7 +3713,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 09:29:01</t>
+          <t>02-03-2026 05:23:00</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3727,7 +3723,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:42</t>
+          <t>02-03-2026 05:21:41</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3747,11 +3743,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26320522785920004701</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26320522773140004645</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>649</t>
@@ -3910,12 +3914,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347611</t>
+          <t>347495</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89776</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3925,17 +3929,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GAEL VALENTIN</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLANUEVA </t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3945,14 +3949,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7203337010</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REP DE NICARAGUA </t>
-        </is>
-      </c>
+          <t>7224977744</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3960,17 +3960,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>02-12-2012</t>
+          <t>12-09-2008</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VALENTINGAEL12@GMAIL.COM</t>
+          <t>LEBE0UF4T@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 14:59:03</t>
+          <t>02-03-2026 10:46:42</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3980,44 +3980,36 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:51</t>
+          <t>02-03-2026 11:29:30</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>02-03-2026 15:04:01</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4025,36 +4017,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26320522796410004796</t>
+          <t>26320522789250004739</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347530</t>
+          <t>347598</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89695</t>
+          <t>89763</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4064,17 +4056,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>ROMINA COLETTE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t xml:space="preserve">CASTELLANO </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ZEPETA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4084,14 +4076,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7225675528</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>CARLOTA</t>
-        </is>
-      </c>
+          <t>7291089200</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4099,17 +4087,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11-01-2006</t>
+          <t>01-04-2008</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>VALERIAZEPETAA1@GMAIL.COM</t>
+          <t>ROMICOLETTE31@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 12:09:14</t>
+          <t>02-03-2026 14:41:09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4119,22 +4107,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 12:37:18</t>
+          <t>02-03-2026 14:50:24</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4144,7 +4132,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:50</t>
+          <t>02-03-2026 14:49:17</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4154,7 +4142,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4164,14 +4152,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26320522791400004759</t>
+          <t>26320522795800004793</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4188,12 +4176,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347992</t>
+          <t>347627</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90157</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4203,17 +4191,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">EUNICE </t>
+          <t xml:space="preserve">FRANCISCO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4223,28 +4211,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7226818060</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>7222502297</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PRIVADA AVELLANO</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18-09-1992</t>
+          <t>20-11-1993</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>EUNICESAN9218@GMAIL.COM</t>
+          <t>FRANCISCO_9320@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>03-03-2026 09:47:15</t>
+          <t>02-03-2026 15:23:41</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4254,36 +4246,44 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-03-2026 09:48:47</t>
+          <t>02-03-2026 19:23:17</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:20:55</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4291,14 +4291,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26320522835410004978</t>
+          <t>26320522816360004905</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4315,12 +4315,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347994</t>
+          <t>347611</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90159</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4330,87 +4330,99 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEMETRIO </t>
+          <t>GAEL VALENTIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALVILLO </t>
+          <t xml:space="preserve">VILLANUEVA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>7203337010</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REP DE NICARAGUA </t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>02-12-2012</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>VALENTINGAEL12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:59:03</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:04:51</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:04:01</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3369637522</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>22-07-1987</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>DEMETRIOCH9287@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:54:17</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 HE</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>3 MESES $2,099</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>699.67</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:57:00</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4418,14 +4430,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26320522835680004982</t>
+          <t>26320522796410004796</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4442,12 +4454,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348036</t>
+          <t>348122</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>90287</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4457,17 +4469,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO</t>
+          <t>ALBERTO DANIEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">RIOS </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RAYON</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4477,12 +4489,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5519545111</t>
+          <t>5654900068</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>BOSQUES DE PIRULES</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4492,17 +4504,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-04-2001</t>
+          <t>14-09-2001</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LUISBRITHIS@GMAIL.COM</t>
+          <t>ALBERTDANY@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 12:54:24</t>
+          <t>03-03-2026 16:33:05</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4512,22 +4524,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 13:06:20</t>
+          <t>03-03-2026 16:50:09</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4537,7 +4549,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-03-2026 13:05:40</t>
+          <t>03-03-2026 16:49:36</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4547,7 +4559,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4557,14 +4569,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26320522839610005033</t>
+          <t>26320522848180005103</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4581,12 +4593,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348126</t>
+          <t>348446</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90291</t>
+          <t>90611</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4596,17 +4608,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN ALBERTO </t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>GARDUÑO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>LOZANO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4616,12 +4628,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7222842150</t>
+          <t>7291005887</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CORREGIDORA2</t>
+          <t>PRIVADA CACERES 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4631,17 +4643,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28-08-1974</t>
+          <t>22-06-2009</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALBERTO2874@HOTMAIL.COM</t>
+          <t>SGARDUNO918@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:02</t>
+          <t>04-03-2026 14:47:25</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4666,17 +4678,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-03-2026 16:48:12</t>
+          <t>04-03-2026 14:57:51</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-03-2026 16:46:41</t>
+          <t>04-03-2026 14:57:12</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4686,7 +4698,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4696,7 +4708,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26320522848120005102</t>
+          <t>26320522884120005313</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4708,24 +4720,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>348268</t>
+          <t>347739</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>89904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4735,17 +4747,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ALDEMAR RAYMUNDO</t>
+          <t>EDUARDO ELHIU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4755,14 +4767,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5623590912</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>MORELOS</t>
-        </is>
-      </c>
+          <t>7292264814</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4770,17 +4778,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-11-1971</t>
+          <t>18-07-1998</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>RAYMUNDOVALDES30@GMAIL.COM</t>
+          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03-03-2026 19:29:01</t>
+          <t>02-03-2026 17:24:34</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4790,44 +4798,36 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>03-03-2026 19:35:47</t>
+          <t>02-03-2026 17:27:05</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:34:01</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4835,14 +4835,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26320522859400005179</t>
+          <t>26320522806550004859</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4859,12 +4859,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>348122</t>
+          <t>347991</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>90156</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ALBERTO DANIEL</t>
+          <t>ABRAHAM MILLEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIOS </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4894,14 +4894,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5654900068</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>BOSQUES DE PIRULES</t>
-        </is>
-      </c>
+          <t>7226508332</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4909,17 +4905,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-09-2001</t>
+          <t>10-08-1999</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALBERTDANY@HOTMAIL.ES</t>
+          <t>HILLELDRUMS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>03-03-2026 16:33:05</t>
+          <t>03-03-2026 09:47:09</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4929,44 +4925,36 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-03-2026 16:50:09</t>
+          <t>03-03-2026 09:49:39</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>03-03-2026 16:49:36</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4974,36 +4962,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26320522848180005103</t>
+          <t>26320522835460004979</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347284</t>
+          <t>331386</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5013,17 +5001,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>NURIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GODINEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5033,14 +5021,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5543692402</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>JARDINES DE SAN MATEO</t>
-        </is>
-      </c>
+          <t>7226873511</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5048,64 +5032,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>03-11-1988</t>
+          <t>01-06-1983</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
+          <t>GGJANY01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>01-03-2026 09:28:32</t>
+          <t>31-12-2025 11:58:13</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>200 la viga tlalnepantla</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 X 2 MESES POR $1,198 METEPEC</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399.33</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>01-03-2026 09:36:17</t>
+          <t>04-03-2026 12:20:13</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>01-03-2026 09:34:02</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5113,14 +5089,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26320522765720004564</t>
+          <t>26320522880420005287</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5137,12 +5113,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347314</t>
+          <t>343681</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5152,17 +5128,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL </t>
+          <t xml:space="preserve">LUIS JESUS </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>DEBEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5172,12 +5148,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7226722765</t>
+          <t>7222287294</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t>SAN ISIDRO 13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5187,17 +5163,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>08-03-2001</t>
+          <t>15-02-1969</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MANULOP632@GMAIL.COM</t>
+          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>01-03-2026 11:10:07</t>
+          <t>14-02-2026 09:58:23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5222,17 +5198,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-03-2026 10:26:20</t>
+          <t>01-03-2026 11:22:35</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>14-02-2026 10:10:26</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5252,19 +5228,11 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26320522787680004716</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
-        </is>
-      </c>
+          <t>26320522767610004596</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>649</t>
@@ -5284,12 +5252,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347316</t>
+          <t>346076</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89481</t>
+          <t>88241</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5299,17 +5267,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EDUARD</t>
+          <t>JAVIER DE JESUS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5319,12 +5287,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7226915455</t>
+          <t>5619333968</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t>5 DE MAYO 712</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5334,17 +5302,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21-10-2003</t>
+          <t>03-03-1990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
+          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:17</t>
+          <t>24-02-2026 07:00:04</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5369,7 +5337,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-03-2026 05:23:00</t>
+          <t>02-03-2026 06:34:23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5379,7 +5347,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>02-03-2026 05:21:41</t>
+          <t>02-03-2026 06:33:27</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5389,7 +5357,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5399,7 +5367,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26320522773140004645</t>
+          <t>26320522780780004667</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5409,7 +5377,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5431,12 +5399,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>347851</t>
+          <t>348758</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>90923</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5446,17 +5414,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RICARDO AXEL</t>
+          <t>HECTOR LEONEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t xml:space="preserve">ORDAZ </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>GALENO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5466,12 +5434,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7227717603</t>
+          <t>5574397936</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
+          <t>FRANCI I MADERO 1917</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5481,17 +5449,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30-09-1993</t>
+          <t>22-12-2009</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>AXELOR.14@GMAIL.COM</t>
+          <t>GALENOLEONEL7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-03-2026 18:48:23</t>
+          <t>05-03-2026 16:55:40</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5516,17 +5484,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:49</t>
+          <t>05-03-2026 17:10:56</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:27</t>
+          <t>05-03-2026 17:07:48</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5536,7 +5504,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5546,7 +5514,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26320522814360004903</t>
+          <t>26320522923140005621</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5558,24 +5526,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>347991</t>
+          <t>347833</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>89998</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5585,17 +5553,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ABRAHAM MILLEL</t>
+          <t>KARLA ISABEL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5605,28 +5573,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7226508332</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>7226289693</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BOSQUE DE CAPULINES</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10-08-1999</t>
+          <t>08-02-1993</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>HILLELDRUMS@GMAIL.COM</t>
+          <t>KARLA080293@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-03-2026 09:47:09</t>
+          <t>02-03-2026 18:34:40</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5636,36 +5608,44 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-03-2026 09:49:39</t>
+          <t>02-03-2026 18:47:06</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:45:03</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5673,36 +5653,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26320522835460004979</t>
+          <t>26320522813850004898</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>347833</t>
+          <t>347851</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>89998</t>
+          <t>90016</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5712,17 +5692,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KARLA ISABEL</t>
+          <t>RICARDO AXEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5732,32 +5712,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7226289693</t>
+          <t>7227717603</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOSQUE DE CAPULINES</t>
+          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>08-02-1993</t>
+          <t>30-09-1993</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>KARLA080293@GMAIL.COM</t>
+          <t>AXELOR.14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:34:40</t>
+          <t>02-03-2026 18:48:23</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5782,7 +5762,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:06</t>
+          <t>02-03-2026 18:52:49</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5792,7 +5772,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:45:03</t>
+          <t>02-03-2026 18:52:27</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5812,7 +5792,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26320522813850004898</t>
+          <t>26320522814360004903</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5836,12 +5816,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>348120</t>
+          <t>347824</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5851,17 +5831,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BRENDA AMPARO</t>
+          <t xml:space="preserve">MONSERRAT </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>PICHARDO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>YEPEZ</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5871,12 +5851,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7221680849</t>
+          <t>7291230160</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IGANACIO ALLENDE 22</t>
+          <t xml:space="preserve">MARIANO MATAMOROS 62 </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5886,17 +5866,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>28-04-1993</t>
+          <t>08-11-2000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BREN_LOP@HOTMAIL.COM</t>
+          <t>PICHLEDES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:29:43</t>
+          <t>02-03-2026 18:28:58</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5911,17 +5891,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:45:46</t>
+          <t>03-03-2026 05:39:04</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5931,7 +5911,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:44:59</t>
+          <t>03-03-2026 05:38:01</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5941,7 +5921,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5951,14 +5931,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26320522847960005100</t>
+          <t>26320522823530004929</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5975,12 +5955,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>347739</t>
+          <t>348443</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>89904</t>
+          <t>90608</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5990,17 +5970,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EDUARDO ELHIU</t>
+          <t>IVAN PABLO ESTEBAN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6010,10 +5990,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7292264814</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>7225501401</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>HIDALGO 7</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6021,17 +6005,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-07-1998</t>
+          <t>18-02-1999</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
+          <t>IVANGUUTZ182@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:34</t>
+          <t>04-03-2026 14:43:17</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6041,36 +6025,44 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:05</t>
+          <t>04-03-2026 15:01:11</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:00:03</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6078,14 +6070,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26320522806550004859</t>
+          <t>26320522884210005316</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6102,12 +6094,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>347938</t>
+          <t>348461</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90103</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6117,17 +6109,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>CLAUDIO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAÑON </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALADO </t>
+          <t>TRANI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6137,10 +6129,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7221689741</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>5531482799</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BARR SANTIAGUITO</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6148,17 +6144,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>11-02-1988</t>
+          <t>23-03-1988</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CARLOS.BALADO@GMAIL.COM</t>
+          <t>ROSATAPROOM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-03-2026 06:15:55</t>
+          <t>04-03-2026 15:28:47</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6168,36 +6164,44 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-03-2026 06:18:50</t>
+          <t>05-03-2026 14:12:55</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:10:07</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6205,22 +6209,2615 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26320522830160004936</t>
+          <t>26320522916700005542</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Hector Fermin  Avalos Montiel</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>347938</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>90103</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAÑON </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BALADO </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>7221689741</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>11-02-1988</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CARLOS.BALADO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:15:55</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1 MES $999</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:18:50</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26320522830160004936</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>347165</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>89330</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AGUSTIN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ALMAZAN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7221565585</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TENANCINGO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14-07-1990</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>AGUS.TOL13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>28-02-2026 09:37:39</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:34:40</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>28-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>28-02-2026 09:50:05</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26320522766810004583</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>347298</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>89463</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ROBERTO AARON</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALINDO </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7225105138</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>GUMERCINDO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>28-02-1988</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ROBERTOGALINDO9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:27:15</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:31:48</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:30:37</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26320522766780004582</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>347525</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>89690</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FERNANDO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ESPINOSA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7222641163</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>JUAN ALDAMA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>07-02-1980</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FME28@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:04:58</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:33:33</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:32:29</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26320522791260004756</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>348444</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>90609</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONCEPCION </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOLINA </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>7227683181</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>JOSEFA ORTIZ</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>21-09-1986</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CONIMR06@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:44:23</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:54:18</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:53:37</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26320522883930005311</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>347994</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>90159</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEMETRIO </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALVILLO </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3369637522</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>22-07-1987</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DEMETRIOCH9287@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:54:17</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:57:00</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26320522835680004982</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>348036</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>90201</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LUIS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>RAYON</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>5519545111</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>02-04-2001</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LUISBRITHIS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>03-03-2026 12:54:24</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:06:20</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:05:40</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26320522839610005033</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>348126</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>90291</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN ALBERTO </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>7222842150</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CORREGIDORA2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>28-08-1974</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>ALBERTO2874@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:38:02</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:48:12</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:46:41</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26320522848120005102</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>348268</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>90433</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ALDEMAR RAYMUNDO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VALDES</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>5623590912</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MORELOS</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>18-11-1971</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>RAYMUNDOVALDES30@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:29:01</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:35:47</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:34:01</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26320522859400005179</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>348120</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>90285</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BRENDA AMPARO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>YEPEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>7221680849</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IGANACIO ALLENDE 22</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>28-04-1993</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>BREN_LOP@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:29:43</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:45:46</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:44:59</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26320522847960005100</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>348349</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>90514</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LUIS RODRIGO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALINAS </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ALCANTARA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7226020278</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>26-04-2006</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>LUISRODRIG900@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:19:48</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:31:12</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:26:08</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26320522875960005237</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Hector Fermin  Avalos Montiel</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>348455</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>90620</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CLAUDIA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7225556154</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>21-10-1994</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CLUDIA.ROA21@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:09:32</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:19:17</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:18:16</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26320522884850005322</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>348535</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>90700</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEONARDO </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAPIA </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7222519086</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>LAZARO MANUEL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>16-06-2009</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LEO.09.TAPIADOM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:41:54</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:46:55</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:45:52</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26320522891860005388</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>348631</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>90796</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERARI MADAI </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANO </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELIZ </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>7321192240</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>07-02-1997</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>MARARICANO72@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:19:40</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:21:28</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26320522910560005469</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>348696</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>90861</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CARLOS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AVILES</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ANGULO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5565378098</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>31-10-1989</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>C.ELITE1@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:43:27</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:53:14</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:52:23</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26320522916230005536</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>347625</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>89790</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LUIS ALONSO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>7227504088</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PRIVADA AVELLANO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>15-09-2011</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>KARLAGABY14@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:21:56</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:30:47</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:29:36</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26320522816940004906</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>348716</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>90881</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GEORGINA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MALANCO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MENDIOLA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>7208221325</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>03-06-1983</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>MALANCOGIGI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:08:46</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:18:06</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:17:34</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26320522918660005572</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Hector Fermin  Avalos Montiel</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>348747</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>90912</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>STEFANIE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MONDRAGON</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>7225761078</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>JUAN ALDAMA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>25-09-1985</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SGUTIERREZMONDRAGON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:33:56</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:48:36</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:47:43</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26320522922060005611</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>347992</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>90157</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EUNICE </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAVARRO </t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>7226818060</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>18-09-1992</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>EUNICESAN9218@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:47:15</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:48:47</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26320522835410004978</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__METEPEC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>331392</t>
+          <t>331386</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANNA JIMENA </t>
+          <t>NURIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LOREDO</t>
+          <t>GODINEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GODINEZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7225941695</t>
+          <t>7226873511</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01-11-2007</t>
+          <t>01-06-1983</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DONA000ROSITA@GMAIL.COM</t>
+          <t>GGJANY01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>31-12-2025 12:03:45</t>
+          <t>31-12-2025 11:58:13</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 12:14:27</t>
+          <t>04-03-2026 12:20:13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26320522880230005286</t>
+          <t>26320522880420005287</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346133</t>
+          <t>336832</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88298</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>EVELYN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7224444385</t>
+          <t>7224667639</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -750,69 +750,61 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>03-10-1960</t>
+          <t>31-07-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GAGUILARM1@GMAIL.COM</t>
+          <t>FLORESTORRESE08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2026 12:15:50</t>
+          <t>21-01-2026 17:33:55</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>200 la viga tlalnepantla</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 X 2 MESES POR $1,198 METEPEC</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399.33</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>05-03-2026 11:31:05</t>
+          <t>06-03-2026 10:44:52</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>05-03-2026 11:30:17</t>
-        </is>
-      </c>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,14 +812,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26320522913700005501</t>
+          <t>26320522946630005755</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +836,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346879</t>
+          <t>346291</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>88456</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ESTEBAN ALBERTO</t>
+          <t xml:space="preserve">ELIDA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">BARROETA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,32 +871,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7226646634</t>
+          <t>5530348605</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERRADA SAN LAURA S/N </t>
+          <t>EUCALIPTO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-06-1992</t>
+          <t>23-04-1990</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>TEBANFAZ0@GMAIL.COM</t>
+          <t>DRA.ALIDABM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-02-2026 08:52:39</t>
+          <t>24-02-2026 18:19:21</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -914,36 +906,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 08:45:55</t>
+          <t>03-03-2026 16:05:15</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>24-02-2026 18:31:40</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -951,22 +951,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26320522833820004965</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>EMMANUEL  GONZALEZ  VILLANUEVA</t>
-        </is>
-      </c>
+          <t>26320522845530005075</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -983,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346131</t>
+          <t>347328</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88296</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLAUDIA </t>
+          <t>BERTHA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BEAS</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ARMAND</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,12 +1010,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7224444382</t>
+          <t>7225522448</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MOCTEZUMA 729</t>
+          <t>GALEANA 432</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,17 +1025,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08-04-1964</t>
+          <t>26-12-1972</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLAUDIA.BARMAND@GMAIL.COM</t>
+          <t>TITILINDA_13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>24-02-2026 12:13:21</t>
+          <t>01-03-2026 12:03:01</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1053,32 +1045,32 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-03-2026 11:28:16</t>
+          <t>01-03-2026 12:08:35</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>05-03-2026 11:25:42</t>
+          <t>01-03-2026 12:07:18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1088,7 +1080,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1098,14 +1090,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26320522913610005500</t>
+          <t>26320522768650004605</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1122,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347333</t>
+          <t>346074</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERIKA JAZMIN </t>
+          <t xml:space="preserve">CARLOS JACINTO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>DEL ANGEL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VALDESPINO</t>
+          <t>BALLESTEROS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,32 +1149,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7224674810</t>
+          <t>7223806506</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CALLE CASCO</t>
+          <t>CALLE CIENTIFICOS 109</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31-08-1984</t>
+          <t>16-06-1980</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ERICKA.JRV@GMAIL.COM</t>
+          <t>CARLOSRO08@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:15:48</t>
+          <t>24-02-2026 06:56:28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1192,22 +1184,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:55</t>
+          <t>02-03-2026 06:28:17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1209,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:19:40</t>
+          <t>02-03-2026 06:27:05</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,14 +1229,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26320522768910004609</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26320522780570004665</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>325426</t>
+          <t>337277</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BRISA ELIZABETH</t>
+          <t>JAEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENITEZ </t>
+          <t>MARURI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENITEZ </t>
+          <t>MARURI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,63 +1296,67 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7223886398</t>
+          <t>7221166978</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MARCELINO SUAREZ</t>
+          <t>EL MOLINO 1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06-12-1987</t>
+          <t>22-03-2001</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BRISBENTZ@GMAIL.COM</t>
+          <t>YAELMARURI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>26-11-2025 13:56:12</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>23-01-2026 14:29:06</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $599 METEPEC</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 17:00:00</t>
+          <t>05-03-2026 14:11:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>26-01-2026 16:46:47</t>
+          <t>05-03-2026 14:10:09</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,36 +1376,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26320522922340005617</t>
+          <t>26320522916610005540</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>327753</t>
+          <t>325426</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS DANIEL </t>
+          <t>BRISA ELIZABETH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1435,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5534444945</t>
+          <t>7223886398</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DIEGO RIVERA 305</t>
+          <t>MARCELINO SUAREZ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-05-1983</t>
+          <t>06-12-1987</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LDANIEL@GMAIL.COM</t>
+          <t>BRISBENTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>06-12-2025 09:36:12</t>
+          <t>26-11-2025 13:56:12</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1477,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-03-2026 11:00:00</t>
+          <t>05-03-2026 17:00:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>06-12-2025 09:42:36</t>
+          <t>26-01-2026 16:46:47</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1497,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1507,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26320522911100005478</t>
+          <t>26320522922340005617</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1519,24 +1523,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>337277</t>
+          <t>327753</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JAEL</t>
+          <t xml:space="preserve">LUIS DANIEL </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MARURI</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARURI</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,12 +1570,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7221166978</t>
+          <t>5534444945</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EL MOLINO 1</t>
+          <t>DIEGO RIVERA 305</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,52 +1585,48 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-03-2001</t>
+          <t>16-05-1983</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YAELMARURI@GMAIL.COM</t>
+          <t>LDANIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>23-01-2026 14:29:06</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 HE</t>
-        </is>
-      </c>
+          <t>06-12-2025 09:36:12</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $599 METEPEC</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 14:11:05</t>
+          <t>05-03-2026 11:00:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>05-03-2026 14:10:09</t>
+          <t>06-12-2025 09:42:36</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26320522916610005540</t>
+          <t>26320522911100005478</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>331392</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88239</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS JACINTO </t>
+          <t xml:space="preserve">DANNA JIMENA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DEL ANGEL</t>
+          <t>LOREDO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BALLESTEROS</t>
+          <t>GODINEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,79 +1705,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7223806506</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CALLE CIENTIFICOS 109</t>
-        </is>
-      </c>
+          <t>7225941695</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16-06-1980</t>
+          <t>01-11-2007</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CARLOSRO08@HOTMAIL.COM</t>
+          <t>DONA000ROSITA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24-02-2026 06:56:28</t>
+          <t>31-12-2025 12:03:45</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>200 la viga tlalnepantla</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 X 2 MESES POR $1,198 METEPEC</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399.33</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:28:17</t>
+          <t>04-03-2026 12:14:27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 06:27:05</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1785,22 +1773,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26320522780570004665</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522880230005286</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1817,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347588</t>
+          <t>346133</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89753</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1832,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAYDI DIANA </t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1852,28 +1832,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7225315083</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>7224444385</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06-10-1988</t>
+          <t>03-10-1960</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LGARCIA@FIRA.GOG</t>
+          <t>GAGUILARM1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 14:25:22</t>
+          <t>24-02-2026 12:15:50</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1883,36 +1867,44 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 14:28:47</t>
+          <t>05-03-2026 11:31:05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>05-03-2026 11:30:17</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1920,14 +1912,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26320522794880004783</t>
+          <t>26320522913700005501</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1944,12 +1936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347345</t>
+          <t>346879</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89510</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1951,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KAREN NAOMI</t>
+          <t>ESTEBAN ALBERTO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDIETA </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>FAZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,32 +1971,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7225360007</t>
+          <t>7226646634</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARETUSA</t>
+          <t xml:space="preserve">CERRADA SAN LAURA S/N </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12-08-2002</t>
+          <t>28-06-1992</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
+          <t>TEBANFAZ0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-03-2026 12:58:59</t>
+          <t>27-02-2026 08:52:39</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2014,12 +2006,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2029,29 +2021,21 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>01-03-2026 13:09:52</t>
+          <t>03-03-2026 08:45:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>01-03-2026 13:08:09</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2059,11 +2043,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26320522769650004617</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26320522833820004965</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>EMMANUEL  GONZALEZ  VILLANUEVA</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2071,24 +2063,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347528</t>
+          <t>343681</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89693</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGE </t>
+          <t xml:space="preserve">LUIS JESUS </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t>DEBEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BANDERAS</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,12 +2110,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7292940204</t>
+          <t>7222287294</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN ALDAMA </t>
+          <t>SAN ISIDRO 13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,17 +2125,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-02-1997</t>
+          <t>15-02-1969</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JORGESALAZAR228@HOTMAIL.COM</t>
+          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:41</t>
+          <t>14-02-2026 09:58:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2153,32 +2145,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:28</t>
+          <t>01-03-2026 11:22:35</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:43</t>
+          <t>14-02-2026 10:10:26</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2198,14 +2190,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26320522790800004750</t>
+          <t>26320522767610004596</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2222,12 +2214,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347561</t>
+          <t>346076</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>88241</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2237,17 +2229,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>JAVIER DE JESUS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISLAS </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2257,12 +2249,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5536313160</t>
+          <t>5619333968</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NAUCAL</t>
+          <t>5 DE MAYO 712</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2272,17 +2264,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02-03-1994</t>
+          <t>03-03-1990</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
+          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 13:19:04</t>
+          <t>24-02-2026 07:00:04</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2292,32 +2284,32 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:44</t>
+          <t>02-03-2026 06:34:23</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:08:36</t>
+          <t>02-03-2026 06:33:27</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2327,7 +2319,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2337,14 +2329,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26320522815880004904</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26320522780780004667</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347300</t>
+          <t>347165</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89465</t>
+          <t>89330</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRMA </t>
+          <t>AGUSTIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBARRAN </t>
+          <t>TOLEDO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>ALMAZAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7221158170</t>
+          <t>7221565585</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PUNGABARATO</t>
+          <t>TENANCINGO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-12-1950</t>
+          <t>14-07-1990</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
+          <t>AGUS.TOL13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:36:01</t>
+          <t>28-02-2026 09:37:39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2431,32 +2431,32 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:45:05</t>
+          <t>01-03-2026 10:34:40</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:43:49</t>
+          <t>28-02-2026 09:50:05</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26320522766920004585</t>
+          <t>26320522766810004583</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2500,12 +2500,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347463</t>
+          <t>347298</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>89463</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELBA SUSANA </t>
+          <t>ROBERTO AARON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IBANCOVICHI</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2535,32 +2535,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7222899520</t>
+          <t>7225105138</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CERRADA DE LUMARAN 118</t>
+          <t>GUMERCINDO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>28-02-1988</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MIBANCOVICHI@GMAIL.COM</t>
+          <t>ROBERTOGALINDO9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:23:35</t>
+          <t>01-03-2026 10:27:15</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:29:01</t>
+          <t>01-03-2026 10:31:48</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:42</t>
+          <t>01-03-2026 10:30:37</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2615,14 +2615,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26320522785920004701</t>
+          <t>26320522766780004582</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>346291</t>
+          <t>347495</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIDA </t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARROETA </t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2674,32 +2674,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5530348605</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>EUCALIPTO</t>
-        </is>
-      </c>
+          <t>7224977744</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23-04-1990</t>
+          <t>12-09-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DRA.ALIDABM@GMAIL.COM</t>
+          <t>LEBE0UF4T@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24-02-2026 18:19:21</t>
+          <t>02-03-2026 10:46:42</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2709,44 +2705,36 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 16:05:15</t>
+          <t>02-03-2026 11:29:30</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>24-02-2026 18:31:40</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2754,36 +2742,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26320522845530005075</t>
+          <t>26320522789250004739</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347328</t>
+          <t>347598</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89493</t>
+          <t>89763</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2793,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BERTHA</t>
+          <t>ROMINA COLETTE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">CASTELLANO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2813,14 +2801,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7225522448</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>GALEANA 432</t>
-        </is>
-      </c>
+          <t>7291089200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2828,17 +2812,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26-12-1972</t>
+          <t>01-04-2008</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TITILINDA_13@HOTMAIL.COM</t>
+          <t>ROMICOLETTE31@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>01-03-2026 12:03:01</t>
+          <t>02-03-2026 14:41:09</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2848,22 +2832,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>01-03-2026 12:08:35</t>
+          <t>02-03-2026 14:50:24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2873,7 +2857,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>01-03-2026 12:07:18</t>
+          <t>02-03-2026 14:49:17</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2883,7 +2867,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2893,36 +2877,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26320522768650004605</t>
+          <t>26320522795800004793</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347317</t>
+          <t>347627</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2932,17 +2916,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ARMANDO ALEJANDRO</t>
+          <t xml:space="preserve">FRANCISCO </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2952,12 +2936,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3310167684</t>
+          <t>7222502297</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALLENDE</t>
+          <t>PRIVADA AVELLANO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2967,17 +2951,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-11-2000</t>
+          <t>20-11-1993</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>AA.SALAZARA@HOTMAIL.COM</t>
+          <t>FRANCISCO_9320@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:43</t>
+          <t>02-03-2026 15:23:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3002,7 +2986,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>01-03-2026 11:18:24</t>
+          <t>02-03-2026 19:23:17</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3012,7 +2996,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>01-03-2026 11:17:37</t>
+          <t>02-03-2026 19:20:55</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3022,7 +3006,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3032,7 +3016,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26320522767540004593</t>
+          <t>26320522816360004905</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3056,12 +3040,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347530</t>
+          <t>347300</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89695</t>
+          <t>89465</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3071,17 +3055,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">IRMA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t xml:space="preserve">ALBARRAN </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ZEPETA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3091,12 +3075,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7225675528</t>
+          <t>7221158170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CARLOTA</t>
+          <t>PUNGABARATO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3106,17 +3090,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11-01-2006</t>
+          <t>24-12-1950</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>VALERIAZEPETAA1@GMAIL.COM</t>
+          <t>IRMAALBARRANCALDERON50@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:09:14</t>
+          <t>01-03-2026 10:36:01</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3126,32 +3110,32 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:37:18</t>
+          <t>01-03-2026 10:45:05</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:50</t>
+          <t>01-03-2026 10:43:49</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3161,7 +3145,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3171,36 +3155,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26320522791400004759</t>
+          <t>26320522766920004585</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>346632</t>
+          <t>347463</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>88797</t>
+          <t>89628</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3210,17 +3194,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">ELBA SUSANA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>IBANCOVICHI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3230,32 +3214,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7224064130</t>
+          <t>7222899520</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE PAULA 58</t>
+          <t>CERRADA DE LUMARAN 118</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01-01-1971</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A.CHAVEZ71@LIVE.COM</t>
+          <t>MIBANCOVICHI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>26-02-2026 05:55:50</t>
+          <t>02-03-2026 09:23:35</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3265,32 +3249,32 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 05:48:40</t>
+          <t>02-03-2026 09:29:01</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-03-2026 05:47:42</t>
+          <t>02-03-2026 09:27:42</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3300,7 +3284,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3310,22 +3294,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26320522823730004932</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522785920004701</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3342,12 +3318,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347284</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3357,17 +3333,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>ARMANDO ALEJANDRO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3377,12 +3353,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5543692402</t>
+          <t>3310167684</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JARDINES DE SAN MATEO</t>
+          <t>ALLENDE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3392,17 +3368,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-11-1988</t>
+          <t>09-11-2000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
+          <t>AA.SALAZARA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>01-03-2026 09:28:32</t>
+          <t>01-03-2026 11:12:43</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3427,17 +3403,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>01-03-2026 09:36:17</t>
+          <t>01-03-2026 11:18:24</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>01-03-2026 09:34:02</t>
+          <t>01-03-2026 11:17:37</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3447,7 +3423,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3457,7 +3433,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26320522765720004564</t>
+          <t>26320522767540004593</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3481,12 +3457,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347314</t>
+          <t>346632</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>88797</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3496,17 +3472,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3516,12 +3492,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7226722765</t>
+          <t>7224064130</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t>SAN FRANCISCO DE PAULA 58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3531,17 +3507,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08-03-2001</t>
+          <t>01-01-1971</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MANULOP632@GMAIL.COM</t>
+          <t>A.CHAVEZ71@LIVE.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>01-03-2026 11:10:07</t>
+          <t>26-02-2026 05:55:50</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3551,22 +3527,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 10:26:20</t>
+          <t>03-03-2026 05:48:40</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3576,7 +3552,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>03-03-2026 05:47:42</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3596,7 +3572,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26320522787680004716</t>
+          <t>26320522823730004932</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3606,12 +3582,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3628,12 +3604,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347316</t>
+          <t>347284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89481</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3643,17 +3619,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EDUARD</t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3663,12 +3639,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7226915455</t>
+          <t>5543692402</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FRESNOS 34</t>
+          <t>JARDINES DE SAN MATEO</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3678,17 +3654,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-10-2003</t>
+          <t>03-11-1988</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
+          <t>EMMANUEL.MARTINEZ@SOLOMEXICANO.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>01-03-2026 11:12:17</t>
+          <t>01-03-2026 09:28:32</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3713,17 +3689,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 05:23:00</t>
+          <t>01-03-2026 09:36:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 05:21:41</t>
+          <t>01-03-2026 09:34:02</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3743,19 +3719,11 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26320522773140004645</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
-        </is>
-      </c>
+          <t>26320522765720004564</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>649</t>
@@ -3775,12 +3743,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347628</t>
+          <t>347314</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89793</t>
+          <t>89479</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3790,17 +3758,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS RAUL </t>
+          <t xml:space="preserve">MANUEL </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3810,12 +3778,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7298256500</t>
+          <t>7226722765</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IGNACIO ALLENDE 22</t>
+          <t>FRESNOS 34</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3825,17 +3793,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-11-1994</t>
+          <t>08-03-2001</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>LUISRAUL.AC@GMAIL.COM</t>
+          <t>MANULOP632@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 15:24:01</t>
+          <t>01-03-2026 11:10:07</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3845,32 +3813,32 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 16:41:32</t>
+          <t>02-03-2026 10:26:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-03-2026 16:40:45</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3890,14 +3858,22 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26320522847660005096</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26320522787680004716</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3914,12 +3890,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347495</t>
+          <t>347316</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>89481</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3929,17 +3905,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>EDUARD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3949,10 +3925,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7224977744</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>7226915455</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FRESNOS 34</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3960,17 +3940,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12-09-2008</t>
+          <t>21-10-2003</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>LEBE0UF4T@GMAIL.COM</t>
+          <t>CONTACTOEDLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 10:46:42</t>
+          <t>01-03-2026 11:12:17</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3980,36 +3960,44 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 11:29:30</t>
+          <t>02-03-2026 05:23:00</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:21:41</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4017,36 +4005,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26320522789250004739</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26320522773140004645</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  URIBE  SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347598</t>
+          <t>347450</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4056,17 +4052,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ROMINA COLETTE</t>
+          <t xml:space="preserve">ROBERTO </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANO </t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4076,28 +4072,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7291089200</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>7225910112</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>URUCOS 633</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01-04-2008</t>
+          <t>02-03-2025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ROMICOLETTE31@GMAIL.COM</t>
+          <t>ROBERTOMR1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:09</t>
+          <t>02-03-2026 08:42:33</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4122,17 +4122,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:24</t>
+          <t>06-03-2026 04:27:03</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 14:49:17</t>
+          <t>06-03-2026 04:25:47</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4152,11 +4152,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26320522795800004793</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26320522933060005693</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>649</t>
@@ -4164,24 +4172,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347627</t>
+          <t>347345</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>89510</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4191,17 +4199,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO </t>
+          <t>KAREN NAOMI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t xml:space="preserve">MENDIETA </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4211,32 +4219,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7222502297</t>
+          <t>7225360007</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t>ARETUSA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20-11-1993</t>
+          <t>12-08-2002</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FRANCISCO_9320@OUTLOOK.COM</t>
+          <t>KAREN.HERNAN2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 15:23:41</t>
+          <t>01-03-2026 12:58:59</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4246,32 +4254,32 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 19:23:17</t>
+          <t>01-03-2026 13:09:52</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-03-2026 19:20:55</t>
+          <t>01-03-2026 13:08:09</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4291,36 +4299,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26320522816360004905</t>
+          <t>26320522769650004617</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347611</t>
+          <t>347528</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89776</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4330,17 +4338,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GAEL VALENTIN</t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLANUEVA </t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>BANDERAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4350,12 +4358,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7203337010</t>
+          <t>7292940204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">REP DE NICARAGUA </t>
+          <t xml:space="preserve">JUAN ALDAMA </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4365,17 +4373,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>02-12-2012</t>
+          <t>28-02-1997</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>VALENTINGAEL12@GMAIL.COM</t>
+          <t>JORGESALAZAR228@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 14:59:03</t>
+          <t>02-03-2026 12:07:41</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4385,32 +4393,32 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:51</t>
+          <t>02-03-2026 12:18:28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:01</t>
+          <t>02-03-2026 12:13:43</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4420,7 +4428,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4430,14 +4438,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26320522796410004796</t>
+          <t>26320522790800004750</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4454,12 +4462,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348122</t>
+          <t>346131</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>88296</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4469,17 +4477,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ALBERTO DANIEL</t>
+          <t xml:space="preserve">CLAUDIA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIOS </t>
+          <t>BEAS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>ARMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4489,32 +4497,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5654900068</t>
+          <t>7224444382</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BOSQUES DE PIRULES</t>
+          <t>MOCTEZUMA 729</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14-09-2001</t>
+          <t>08-04-1964</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ALBERTDANY@HOTMAIL.ES</t>
+          <t>CLAUDIA.BARMAND@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:33:05</t>
+          <t>24-02-2026 12:13:21</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4539,17 +4547,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:50:09</t>
+          <t>05-03-2026 11:28:16</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:49:36</t>
+          <t>05-03-2026 11:25:42</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4569,7 +4577,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26320522848180005103</t>
+          <t>26320522913610005500</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4581,24 +4589,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>347333</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4608,17 +4616,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">ERIKA JAZMIN </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GARDUÑO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOZANO</t>
+          <t>VALDESPINO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4628,32 +4636,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7291005887</t>
+          <t>7224674810</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PRIVADA CACERES 2</t>
+          <t>CALLE CASCO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-06-2009</t>
+          <t>31-08-1984</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SGARDUNO918@GMAIL.COM</t>
+          <t>ERICKA.JRV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>04-03-2026 14:47:25</t>
+          <t>01-03-2026 12:15:48</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4663,32 +4671,32 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>04-03-2026 14:57:51</t>
+          <t>01-03-2026 12:21:55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>04-03-2026 14:57:12</t>
+          <t>01-03-2026 12:19:40</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4708,14 +4716,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26320522884120005313</t>
+          <t>26320522768910004609</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4732,12 +4740,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347739</t>
+          <t>347525</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89904</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4747,17 +4755,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EDUARDO ELHIU</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4767,10 +4775,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7292264814</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>7222641163</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>JUAN ALDAMA</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4778,17 +4790,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-07-1998</t>
+          <t>07-02-1980</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
+          <t>FME28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:34</t>
+          <t>02-03-2026 12:04:58</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4798,36 +4810,44 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:05</t>
+          <t>02-03-2026 12:33:33</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:32:29</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4835,36 +4855,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26320522806550004859</t>
+          <t>26320522791260004756</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347991</t>
+          <t>347625</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>89790</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4874,17 +4894,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ABRAHAM MILLEL</t>
+          <t xml:space="preserve"> LUIS ALONSO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4914,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7226508332</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>7227504088</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PRIVADA AVELLANO</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4905,17 +4929,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10-08-1999</t>
+          <t>15-09-2011</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>HILLELDRUMS@GMAIL.COM</t>
+          <t>KARLAGABY14@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>03-03-2026 09:47:09</t>
+          <t>02-03-2026 15:21:56</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4925,36 +4949,44 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-03-2026 09:49:39</t>
+          <t>02-03-2026 19:30:47</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:29:36</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4962,14 +4994,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26320522835460004979</t>
+          <t>26320522816940004906</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4986,12 +5018,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>331386</t>
+          <t>347824</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5001,17 +5033,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NURIA</t>
+          <t xml:space="preserve">MONSERRAT </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GODINEZ</t>
+          <t>PICHARDO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>LEDESMA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5021,67 +5053,79 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7226873511</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>7291230160</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANO MATAMOROS 62 </t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01-06-1983</t>
+          <t>08-11-2000</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>GGJANY01@GMAIL.COM</t>
+          <t>PICHLEDES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>31-12-2025 11:58:13</t>
+          <t>02-03-2026 18:28:58</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>200 la viga tlalnepantla</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3 X 2 MESES POR $1,198 METEPEC</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>399.33</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>04-03-2026 12:20:13</t>
+          <t>03-03-2026 05:39:04</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:38:01</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5089,14 +5133,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26320522880420005287</t>
+          <t>26320522823530004929</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5113,12 +5157,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343681</t>
+          <t>347905</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>90070</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5128,17 +5172,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS JESUS </t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DEBEZ</t>
+          <t>COLIN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5148,12 +5192,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7222287294</t>
+          <t>7224122342</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SAN ISIDRO 13</t>
+          <t>LEONAVCARIO 409</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5163,17 +5207,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-02-1969</t>
+          <t>01-04-1986</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LDERBEZ@BECOMARDEMEXICO.COM</t>
+          <t>ROLLERCOLDVILLANUEVA@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>14-02-2026 09:58:23</t>
+          <t>02-03-2026 20:36:21</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5198,17 +5242,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>01-03-2026 11:22:35</t>
+          <t>08-03-2026 12:03:11</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>14-02-2026 10:10:26</t>
+          <t>08-03-2026 12:01:45</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5218,7 +5262,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5228,7 +5272,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26320522767610004596</t>
+          <t>26320522985540006085</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5252,12 +5296,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>346076</t>
+          <t>347561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88241</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5267,17 +5311,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JAVIER DE JESUS</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">ISLAS </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5287,12 +5331,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5619333968</t>
+          <t>5536313160</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5 DE MAYO 712</t>
+          <t>NAUCAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5302,17 +5346,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-03-1990</t>
+          <t>02-03-1994</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JESUS.ALCANTARA109@GMAIL.COM</t>
+          <t>JONATHANISLASCORTES1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>24-02-2026 07:00:04</t>
+          <t>02-03-2026 13:19:04</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5322,32 +5366,32 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-03-2026 06:34:23</t>
+          <t>02-03-2026 19:15:44</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>02-03-2026 06:33:27</t>
+          <t>02-03-2026 19:08:36</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5357,7 +5401,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5367,22 +5411,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26320522780780004667</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
-        </is>
-      </c>
+          <t>26320522815880004904</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5399,12 +5435,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>348758</t>
+          <t>347739</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90923</t>
+          <t>89904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5414,17 +5450,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HECTOR LEONEL</t>
+          <t>EDUARDO ELHIU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORDAZ </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GALENO</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5434,14 +5470,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5574397936</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>FRANCI I MADERO 1917</t>
-        </is>
-      </c>
+          <t>7292264814</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5449,17 +5481,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22-12-2009</t>
+          <t>18-07-1998</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>GALENOLEONEL7@GMAIL.COM</t>
+          <t>VALENCIA.ALAVAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>05-03-2026 16:55:40</t>
+          <t>02-03-2026 17:24:34</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5469,44 +5501,36 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>05-03-2026 17:10:56</t>
+          <t>02-03-2026 17:27:05</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>05-03-2026 17:07:48</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5514,14 +5538,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26320522923140005621</t>
+          <t>26320522806550004859</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5538,12 +5562,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>347833</t>
+          <t>347628</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89998</t>
+          <t>89793</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5553,17 +5577,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KARLA ISABEL</t>
+          <t xml:space="preserve">LUIS RAUL </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5573,32 +5597,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7226289693</t>
+          <t>7298256500</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>BOSQUE DE CAPULINES</t>
+          <t>IGNACIO ALLENDE 22</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>08-02-1993</t>
+          <t>26-11-1994</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>KARLA080293@GMAIL.COM</t>
+          <t>LUISRAUL.AC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:34:40</t>
+          <t>02-03-2026 15:24:01</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5608,22 +5632,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:47:06</t>
+          <t>03-03-2026 16:41:32</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5633,7 +5657,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:45:03</t>
+          <t>03-03-2026 16:40:45</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5643,7 +5667,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5653,36 +5677,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26320522813850004898</t>
+          <t>26320522847660005096</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>347851</t>
+          <t>347611</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5692,17 +5716,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RICARDO AXEL</t>
+          <t>GAEL VALENTIN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t xml:space="preserve">VILLANUEVA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5712,12 +5736,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7227717603</t>
+          <t>7203337010</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
+          <t xml:space="preserve">REP DE NICARAGUA </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5727,17 +5751,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30-09-1993</t>
+          <t>02-12-2012</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>AXELOR.14@GMAIL.COM</t>
+          <t>VALENTINGAEL12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:48:23</t>
+          <t>02-03-2026 14:59:03</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5762,17 +5786,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:49</t>
+          <t>02-03-2026 15:04:51</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:52:27</t>
+          <t>02-03-2026 15:04:01</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5792,7 +5816,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26320522814360004903</t>
+          <t>26320522796410004796</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5804,24 +5828,24 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>347824</t>
+          <t>347530</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>89989</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5831,17 +5855,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONSERRAT </t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PICHARDO</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LEDESMA</t>
+          <t>ZEPETA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5851,12 +5875,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7291230160</t>
+          <t>7225675528</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANO MATAMOROS 62 </t>
+          <t>CARLOTA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5866,17 +5890,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>08-11-2000</t>
+          <t>11-01-2006</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PICHLEDES@GMAIL.COM</t>
+          <t>VALERIAZEPETAA1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>02-03-2026 18:28:58</t>
+          <t>02-03-2026 12:09:14</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5891,27 +5915,27 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 05:39:04</t>
+          <t>02-03-2026 12:37:18</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-03-2026 05:38:01</t>
+          <t>02-03-2026 12:36:50</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5921,7 +5945,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5931,36 +5955,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26320522823530004929</t>
+          <t>26320522791400004759</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348443</t>
+          <t>347992</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90608</t>
+          <t>90157</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5970,17 +5994,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IVAN PABLO ESTEBAN</t>
+          <t xml:space="preserve">EUNICE </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5990,32 +6014,28 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7225501401</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>HIDALGO 7</t>
-        </is>
-      </c>
+          <t>7226818060</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-02-1999</t>
+          <t>18-09-1992</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>IVANGUUTZ182@GMAIL.COM</t>
+          <t>EUNICESAN9218@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-03-2026 14:43:17</t>
+          <t>03-03-2026 09:47:15</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6025,44 +6045,36 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>04-03-2026 15:01:11</t>
+          <t>03-03-2026 09:48:47</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>04-03-2026 15:00:03</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6070,14 +6082,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26320522884210005316</t>
+          <t>26320522835410004978</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6094,12 +6106,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>348461</t>
+          <t>347994</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>90159</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6109,34 +6121,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CLAUDIO</t>
+          <t xml:space="preserve">DEMETRIO </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">CALVILLO </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRANI</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5531482799</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>BARR SANTIAGUITO</t>
-        </is>
-      </c>
+          <t>3369637522</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6144,17 +6152,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-03-1988</t>
+          <t>22-07-1987</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ROSATAPROOM@GMAIL.COM</t>
+          <t>DEMETRIOCH9287@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>04-03-2026 15:28:47</t>
+          <t>03-03-2026 09:54:17</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6164,44 +6172,36 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>05-03-2026 14:12:55</t>
+          <t>03-03-2026 09:57:00</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>05-03-2026 14:10:07</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6209,36 +6209,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26320522916700005542</t>
+          <t>26320522835680004982</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>347938</t>
+          <t>348036</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90103</t>
+          <t>90201</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>LUIS EDUARDO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAÑON </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALADO </t>
+          <t>RAYON</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6268,10 +6268,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7221689741</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>5519545111</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6279,17 +6283,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>11-02-1988</t>
+          <t>02-04-2001</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CARLOS.BALADO@GMAIL.COM</t>
+          <t>LUISBRITHIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-03-2026 06:15:55</t>
+          <t>03-03-2026 12:54:24</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6299,36 +6303,44 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-03-2026 06:18:50</t>
+          <t>03-03-2026 13:06:20</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:05:40</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6336,36 +6348,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26320522830160004936</t>
+          <t>26320522839610005033</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>347165</t>
+          <t>348126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>89330</t>
+          <t>90291</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6375,17 +6387,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t xml:space="preserve">JUAN ALBERTO </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TOLEDO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ALMAZAN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6395,32 +6407,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7221565585</t>
+          <t>7222842150</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>CORREGIDORA2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14-07-1990</t>
+          <t>28-08-1974</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>AGUS.TOL13@GMAIL.COM</t>
+          <t>ALBERTO2874@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>28-02-2026 09:37:39</t>
+          <t>03-03-2026 16:38:02</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6430,32 +6442,32 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>01-03-2026 10:34:40</t>
+          <t>03-03-2026 16:48:12</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>28-03-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>28-02-2026 09:50:05</t>
+          <t>03-03-2026 16:46:41</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6465,7 +6477,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6475,36 +6487,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26320522766810004583</t>
+          <t>26320522848120005102</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>347298</t>
+          <t>347938</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>90103</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6514,17 +6526,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ROBERTO AARON</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t xml:space="preserve">MAÑON </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">BALADO </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6534,14 +6546,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7225105138</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>GUMERCINDO</t>
-        </is>
-      </c>
+          <t>7221689741</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6549,17 +6557,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>28-02-1988</t>
+          <t>11-02-1988</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ROBERTOGALINDO9@GMAIL.COM</t>
+          <t>CARLOS.BALADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>01-03-2026 10:27:15</t>
+          <t>03-03-2026 06:15:55</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6569,44 +6577,36 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:48</t>
+          <t>03-03-2026 06:18:50</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:30:37</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6614,14 +6614,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26320522766780004582</t>
+          <t>26320522830160004936</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6638,12 +6638,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>347525</t>
+          <t>347833</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>89690</t>
+          <t>89998</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6653,17 +6653,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>KARLA ISABEL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6673,32 +6673,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7222641163</t>
+          <t>7226289693</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>JUAN ALDAMA</t>
+          <t>BOSQUE DE CAPULINES</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>07-02-1980</t>
+          <t>08-02-1993</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>FME28@HOTMAIL.COM</t>
+          <t>KARLA080293@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>02-03-2026 12:04:58</t>
+          <t>02-03-2026 18:34:40</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6708,32 +6708,32 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>02-03-2026 12:33:33</t>
+          <t>02-03-2026 18:47:06</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>02-03-2026 12:32:29</t>
+          <t>02-03-2026 18:45:03</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6753,14 +6753,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26320522791260004756</t>
+          <t>26320522813850004898</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6777,12 +6777,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>348444</t>
+          <t>347991</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90609</t>
+          <t>90156</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONCEPCION </t>
+          <t>ABRAHAM MILLEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINA </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6812,32 +6812,28 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7227683181</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>JOSEFA ORTIZ</t>
-        </is>
-      </c>
+          <t>7226508332</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21-09-1986</t>
+          <t>10-08-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CONIMR06@GMAIL.COM</t>
+          <t>HILLELDRUMS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>04-03-2026 14:44:23</t>
+          <t>03-03-2026 09:47:09</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6847,44 +6843,36 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>04-03-2026 14:54:18</t>
+          <t>03-03-2026 09:49:39</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>04-03-2026 14:53:37</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6892,14 +6880,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26320522883930005311</t>
+          <t>26320522835460004979</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6916,12 +6904,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>347994</t>
+          <t>347851</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90159</t>
+          <t>90016</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6931,87 +6919,99 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEMETRIO </t>
+          <t>RICARDO AXEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALVILLO </t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>7227717603</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSQUES DE CAPULINES </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>30-09-1993</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>AXELOR.14@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:48:23</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:52:49</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:52:27</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>3369637522</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>22-07-1987</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>DEMETRIOCH9287@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:54:17</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 HE</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>3 MESES $2,099</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>699.67</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:57:00</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7019,36 +7019,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26320522835680004982</t>
+          <t>26320522814360004903</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>348036</t>
+          <t>347588</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO</t>
+          <t xml:space="preserve">LAYDI DIANA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RAYON</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7078,32 +7078,28 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5519545111</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>METEPEC</t>
-        </is>
-      </c>
+          <t>7225315083</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>02-04-2001</t>
+          <t>06-10-1988</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LUISBRITHIS@GMAIL.COM</t>
+          <t>LGARCIA@FIRA.GOG</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-03-2026 12:54:24</t>
+          <t>02-03-2026 14:25:22</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7113,44 +7109,36 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-03-2026 13:06:20</t>
+          <t>02-03-2026 14:28:47</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>03-03-2026 13:05:40</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7158,36 +7146,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26320522839610005033</t>
+          <t>26320522794880004783</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>348126</t>
+          <t>348268</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90291</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7197,17 +7185,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN ALBERTO </t>
+          <t>ALDEMAR RAYMUNDO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VALDES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7217,12 +7205,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7222842150</t>
+          <t>5623590912</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CORREGIDORA2</t>
+          <t>MORELOS</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7232,17 +7220,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>28-08-1974</t>
+          <t>18-11-1971</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ALBERTO2874@HOTMAIL.COM</t>
+          <t>RAYMUNDOVALDES30@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:02</t>
+          <t>03-03-2026 19:29:01</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7267,17 +7255,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>03-03-2026 16:48:12</t>
+          <t>03-03-2026 19:35:47</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>03-03-2026 16:46:41</t>
+          <t>03-03-2026 19:34:01</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7287,7 +7275,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7297,7 +7285,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26320522848120005102</t>
+          <t>26320522859400005179</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7321,12 +7309,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>348268</t>
+          <t>348535</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>90700</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7336,17 +7324,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ALDEMAR RAYMUNDO</t>
+          <t xml:space="preserve">LEONARDO </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">TAPIA </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7356,12 +7344,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5623590912</t>
+          <t>7222519086</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>LAZARO MANUEL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7371,17 +7359,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18-11-1971</t>
+          <t>16-06-2009</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RAYMUNDOVALDES30@GMAIL.COM</t>
+          <t>LEO.09.TAPIADOM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>03-03-2026 19:29:01</t>
+          <t>04-03-2026 17:41:54</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7406,7 +7394,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>03-03-2026 19:35:47</t>
+          <t>04-03-2026 17:46:55</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7416,7 +7404,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>03-03-2026 19:34:01</t>
+          <t>04-03-2026 17:45:52</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7426,7 +7414,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7436,7 +7424,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26320522859400005179</t>
+          <t>26320522891860005388</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7460,12 +7448,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>348120</t>
+          <t>348631</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>90796</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7475,17 +7463,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BRENDA AMPARO</t>
+          <t xml:space="preserve">MERARI MADAI </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">CANO </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>YEPEZ</t>
+          <t xml:space="preserve">TELIZ </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7495,14 +7483,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7221680849</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>IGANACIO ALLENDE 22</t>
-        </is>
-      </c>
+          <t>7321192240</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7510,17 +7494,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28-04-1993</t>
+          <t>07-02-1997</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BREN_LOP@HOTMAIL.COM</t>
+          <t>MARARICANO72@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>03-03-2026 16:29:43</t>
+          <t>05-03-2026 08:19:40</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7530,44 +7514,36 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-03-2026 16:45:46</t>
+          <t>05-03-2026 08:21:28</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>03-03-2026 16:44:59</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7575,14 +7551,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26320522847960005100</t>
+          <t>26320522910560005469</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7599,12 +7575,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>348349</t>
+          <t>348120</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90514</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7614,17 +7590,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LUIS RODRIGO</t>
+          <t>BRENDA AMPARO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALINAS </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ALCANTARA</t>
+          <t>YEPEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7634,32 +7610,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7226020278</t>
+          <t>7221680849</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>IGANACIO ALLENDE 22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>26-04-2006</t>
+          <t>28-04-1993</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>LUISRODRIG900@GMAIL.COM</t>
+          <t>BREN_LOP@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>04-03-2026 08:19:48</t>
+          <t>03-03-2026 16:29:43</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7684,17 +7660,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>04-03-2026 08:31:12</t>
+          <t>03-03-2026 16:45:46</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>04-03-2026 08:26:08</t>
+          <t>03-03-2026 16:44:59</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7704,7 +7680,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7714,7 +7690,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26320522875960005237</t>
+          <t>26320522847960005100</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7726,24 +7702,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Hector Fermin  Avalos Montiel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>348455</t>
+          <t>348349</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90620</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7753,17 +7729,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CLAUDIA ESPERANZA</t>
+          <t>LUIS RODRIGO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t xml:space="preserve">SALINAS </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ALCANTARA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7773,7 +7749,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7225556154</t>
+          <t>7226020278</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7783,22 +7759,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21-10-1994</t>
+          <t>26-04-2006</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLUDIA.ROA21@HOTMAIL.COM</t>
+          <t>LUISRODRIG900@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>04-03-2026 15:09:32</t>
+          <t>04-03-2026 08:19:48</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7823,17 +7799,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>04-03-2026 15:19:17</t>
+          <t>04-03-2026 08:31:12</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>04-03-2026 15:18:16</t>
+          <t>04-03-2026 08:26:08</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7843,7 +7819,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7853,7 +7829,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26320522884850005322</t>
+          <t>26320522875960005237</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7865,24 +7841,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>348535</t>
+          <t>348444</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>90700</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7892,17 +7868,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONARDO </t>
+          <t xml:space="preserve">CONCEPCION </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIA </t>
+          <t xml:space="preserve">MOLINA </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7912,32 +7888,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7222519086</t>
+          <t>7227683181</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LAZARO MANUEL</t>
+          <t>JOSEFA ORTIZ</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>16-06-2009</t>
+          <t>21-09-1986</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>LEO.09.TAPIADOM@GMAIL.COM</t>
+          <t>CONIMR06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>04-03-2026 17:41:54</t>
+          <t>04-03-2026 14:44:23</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7962,17 +7938,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>04-03-2026 17:46:55</t>
+          <t>04-03-2026 14:54:18</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>04-03-2026 17:45:52</t>
+          <t>04-03-2026 14:53:37</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7992,7 +7968,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26320522891860005388</t>
+          <t>26320522883930005311</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -8004,24 +7980,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>348631</t>
+          <t>348443</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>90608</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8031,17 +8007,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERARI MADAI </t>
+          <t>IVAN PABLO ESTEBAN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANO </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TELIZ </t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8051,28 +8027,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7321192240</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>7225501401</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>HIDALGO 7</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>07-02-1997</t>
+          <t>18-02-1999</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>MARARICANO72@GMAIL.COM</t>
+          <t>IVANGUUTZ182@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>05-03-2026 08:19:40</t>
+          <t>04-03-2026 14:43:17</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8082,36 +8062,44 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>05-03-2026 08:21:28</t>
+          <t>04-03-2026 15:01:11</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:00:03</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8119,14 +8107,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26320522910560005469</t>
+          <t>26320522884210005316</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8143,12 +8131,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>348696</t>
+          <t>348461</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90861</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8158,17 +8146,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>CLAUDIO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>TRANI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8178,12 +8166,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5565378098</t>
+          <t>5531482799</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>BARR SANTIAGUITO</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8193,17 +8181,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31-10-1989</t>
+          <t>23-03-1988</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>C.ELITE1@HOTMAIL.COM</t>
+          <t>ROSATAPROOM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>05-03-2026 13:43:27</t>
+          <t>04-03-2026 15:28:47</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8213,32 +8201,32 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>05-03-2026 13:53:14</t>
+          <t>05-03-2026 14:12:55</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>05-03-2026 13:52:23</t>
+          <t>05-03-2026 14:10:07</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8258,36 +8246,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26320522916230005536</t>
+          <t>26320522916700005542</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Fermin  Avalos Montiel</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>347625</t>
+          <t>348696</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>89790</t>
+          <t>90861</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8297,17 +8285,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUIS ALONSO</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8317,12 +8305,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7227504088</t>
+          <t>5565378098</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PRIVADA AVELLANO</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8332,17 +8320,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>15-09-2011</t>
+          <t>31-10-1989</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KARLAGABY14@HOTMAIL.COM</t>
+          <t>C.ELITE1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:56</t>
+          <t>05-03-2026 13:43:27</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8352,32 +8340,32 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>02-03-2026 19:30:47</t>
+          <t>05-03-2026 13:53:14</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>02-03-2026 19:29:36</t>
+          <t>05-03-2026 13:52:23</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8387,7 +8375,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8397,14 +8385,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26320522816940004906</t>
+          <t>26320522916230005536</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8511,7 +8499,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -8560,12 +8548,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>348747</t>
+          <t>349218</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90912</t>
+          <t>91383</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8575,17 +8563,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>STEFANIE</t>
+          <t xml:space="preserve">LUZ ARERI </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>VALDIVIA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MONDRAGON</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8595,12 +8583,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7225761078</t>
+          <t>7292781056</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JUAN ALDAMA</t>
+          <t>ATZAPOTZALTONGO 17</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8610,17 +8598,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>25-09-1985</t>
+          <t>07-10-1974</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>SGUTIERREZMONDRAGON@GMAIL.COM</t>
+          <t>LUZERERI_VALDIVIA@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>05-03-2026 16:33:56</t>
+          <t>08-03-2026 11:49:46</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8630,32 +8618,32 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>05-03-2026 16:48:36</t>
+          <t>08-03-2026 11:55:46</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>05-03-2026 16:47:43</t>
+          <t>08-03-2026 11:54:38</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8675,14 +8663,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26320522922060005611</t>
+          <t>26320522985360006079</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8699,12 +8687,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>347992</t>
+          <t>348928</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90157</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8714,17 +8702,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">EUNICE </t>
+          <t>MONICA IXCHEL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8734,10 +8722,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7226818060</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>7223714629</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8745,17 +8737,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18-09-1992</t>
+          <t>30-12-2003</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>EUNICESAN9218@GMAIL.COM</t>
+          <t>MONICIXCHEL345@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>03-03-2026 09:47:15</t>
+          <t>06-03-2026 15:13:50</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8765,36 +8757,44 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>03-03-2026 09:48:47</t>
+          <t>06-03-2026 15:25:36</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:24:48</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8802,22 +8802,1559 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26320522835410004978</t>
+          <t>26320522952560005826</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>349150</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>91315</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GERMAN ALBERTO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VENEGAS </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>7223949886</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>28-09-1990</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>GAVE_ANG@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:35:42</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:45:10</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:44:29</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26320522975150006013</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>348455</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>90620</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CLAUDIA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>7225556154</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>21-10-1994</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>CLUDIA.ROA21@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:09:32</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:19:17</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:18:16</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26320522884850005322</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>348747</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>90912</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>STEFANIE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MONDRAGON</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>7225761078</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>JUAN ALDAMA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>25-09-1985</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SGUTIERREZMONDRAGON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:33:56</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:48:36</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:47:43</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26320522922060005611</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>349236</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>91401</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IRINA </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ABUZGILDINA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>5618761209</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LEON AVICARIO 476</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>24-01-1985</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>THEO@INBOEX.RU</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>08-03-2026 12:42:30</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>08-03-2026 12:48:47</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>08-03-2026 12:47:52</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26320522986250006097</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>348607</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>90772</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIANA ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILCHIS </t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>7225680465</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>URUCOS 633</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>23-09-1991</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ALE-GARCIAVILCHIS27@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:15:47</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>06-03-2026 04:31:00</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>06-03-2026 04:29:51</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26320522933120005695</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>JESSICA GABRIELA DOMINGUEZ  ESCOBAR</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>348991</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>91156</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOKSAN </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>7229809569</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CITLALI 1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>02-11-2004</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>JOKSANCUBE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:21:30</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:31:12</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:30:07</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26320522956630005873</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>349173</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>91338</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUARDO </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>5546345918</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ESTADO DE MEXICO 3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>30-10-2006</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>EDDIEMGZZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>08-03-2026 09:23:31</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>08-03-2026 09:38:16</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>08-03-2026 09:32:36</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26320522983170006029</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>349198</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>91363</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERVEY DAVID </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARZA </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>7291439551</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARICUTIN 21 </t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>30-11-1999</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>ARVEYR8@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>08-03-2026 10:39:29</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>08-03-2026 10:45:01</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>08-03-2026 10:43:58</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26320522984220006048</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>348122</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>90287</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ALBERTO DANIEL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIOS </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CHAPARRO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>5654900068</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>BOSQUES DE PIRULES</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>14-09-2001</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>ALBERTDANY@HOTMAIL.ES</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:33:05</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:50:09</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:49:36</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26320522848180005103</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Erick Rodolfo Garduño Gomez Tagle</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>348446</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>90611</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>GARDUÑO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>LOZANO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>7291005887</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PRIVADA CACERES 2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>22-06-2009</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SGARDUNO918@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:47:25</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:57:51</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:57:12</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26320522884120005313</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>348758</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>90923</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HECTOR LEONEL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORDAZ </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GALENO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>5574397936</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>FRANCI I MADERO 1917</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>22-12-2009</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>GALENOLEONEL7@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:55:40</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:10:56</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:07:48</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26320522923140005621</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
